--- a/00_Data/Raw/Wind_Series/Governador Dix-Sept Rosado.xlsx
+++ b/00_Data/Raw/Wind_Series/Governador Dix-Sept Rosado.xlsx
@@ -6,28 +6,27 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t xml:space="preserve">Data</t>
+    <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Geração</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vento</t>
+    <t xml:space="preserve">Wind_speed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -64,7 +63,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -362,18 +361,12 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>30682</v>
       </c>
       <c r="B2" t="n">
-        <v>0.500461021505376</v>
-      </c>
-      <c r="C2" t="n">
         <v>7.34026747311828</v>
       </c>
     </row>
@@ -382,9 +375,6 @@
         <v>30713</v>
       </c>
       <c r="B3" t="n">
-        <v>0.478168103448276</v>
-      </c>
-      <c r="C3" t="n">
         <v>7.12929454022988</v>
       </c>
     </row>
@@ -393,9 +383,6 @@
         <v>30742</v>
       </c>
       <c r="B4" t="n">
-        <v>0.252154569892473</v>
-      </c>
-      <c r="C4" t="n">
         <v>5.30015456989247</v>
       </c>
     </row>
@@ -404,9 +391,6 @@
         <v>30773</v>
       </c>
       <c r="B5" t="n">
-        <v>0.187788888888889</v>
-      </c>
-      <c r="C5" t="n">
         <v>4.6935625</v>
       </c>
     </row>
@@ -415,9 +399,6 @@
         <v>30803</v>
       </c>
       <c r="B6" t="n">
-        <v>0.291002688172043</v>
-      </c>
-      <c r="C6" t="n">
         <v>5.64965053763441</v>
       </c>
     </row>
@@ -426,9 +407,6 @@
         <v>30834</v>
       </c>
       <c r="B7" t="n">
-        <v>0.442779166666667</v>
-      </c>
-      <c r="C7" t="n">
         <v>6.79520277777778</v>
       </c>
     </row>
@@ -437,9 +415,6 @@
         <v>30864</v>
       </c>
       <c r="B8" t="n">
-        <v>0.513208333333333</v>
-      </c>
-      <c r="C8" t="n">
         <v>7.30352016129032</v>
       </c>
     </row>
@@ -448,9 +423,6 @@
         <v>30895</v>
       </c>
       <c r="B9" t="n">
-        <v>0.577798387096774</v>
-      </c>
-      <c r="C9" t="n">
         <v>7.84197043010753</v>
       </c>
     </row>
@@ -459,9 +431,6 @@
         <v>30926</v>
       </c>
       <c r="B10" t="n">
-        <v>0.615730555555556</v>
-      </c>
-      <c r="C10" t="n">
         <v>8.18343194444444</v>
       </c>
     </row>
@@ -470,9 +439,6 @@
         <v>30956</v>
       </c>
       <c r="B11" t="n">
-        <v>0.670040322580645</v>
-      </c>
-      <c r="C11" t="n">
         <v>8.73987768817204</v>
       </c>
     </row>
@@ -481,9 +447,6 @@
         <v>30987</v>
       </c>
       <c r="B12" t="n">
-        <v>0.660634722222222</v>
-      </c>
-      <c r="C12" t="n">
         <v>8.64287083333333</v>
       </c>
     </row>
@@ -492,9 +455,6 @@
         <v>31017</v>
       </c>
       <c r="B13" t="n">
-        <v>0.600974462365591</v>
-      </c>
-      <c r="C13" t="n">
         <v>8.08908198924731</v>
       </c>
     </row>
@@ -503,9 +463,6 @@
         <v>31048</v>
       </c>
       <c r="B14" t="n">
-        <v>0.346306451612903</v>
-      </c>
-      <c r="C14" t="n">
         <v>5.9895752688172</v>
       </c>
     </row>
@@ -514,9 +471,6 @@
         <v>31079</v>
       </c>
       <c r="B15" t="n">
-        <v>0.237505952380952</v>
-      </c>
-      <c r="C15" t="n">
         <v>5.16384226190476</v>
       </c>
     </row>
@@ -525,9 +479,6 @@
         <v>31107</v>
       </c>
       <c r="B16" t="n">
-        <v>0.226202956989247</v>
-      </c>
-      <c r="C16" t="n">
         <v>5.03957392473118</v>
       </c>
     </row>
@@ -536,9 +487,6 @@
         <v>31138</v>
       </c>
       <c r="B17" t="n">
-        <v>0.146547222222222</v>
-      </c>
-      <c r="C17" t="n">
         <v>4.10041805555556</v>
       </c>
     </row>
@@ -547,9 +495,6 @@
         <v>31168</v>
       </c>
       <c r="B18" t="n">
-        <v>0.303227150537634</v>
-      </c>
-      <c r="C18" t="n">
         <v>5.67683467741935</v>
       </c>
     </row>
@@ -558,9 +503,6 @@
         <v>31199</v>
       </c>
       <c r="B19" t="n">
-        <v>0.339981944444444</v>
-      </c>
-      <c r="C19" t="n">
         <v>5.97847361111111</v>
       </c>
     </row>
@@ -569,9 +511,6 @@
         <v>31229</v>
       </c>
       <c r="B20" t="n">
-        <v>0.514241935483871</v>
-      </c>
-      <c r="C20" t="n">
         <v>7.31987096774194</v>
       </c>
     </row>
@@ -580,9 +519,6 @@
         <v>31260</v>
       </c>
       <c r="B21" t="n">
-        <v>0.573911290322581</v>
-      </c>
-      <c r="C21" t="n">
         <v>7.78036424731183</v>
       </c>
     </row>
@@ -591,9 +527,6 @@
         <v>31291</v>
       </c>
       <c r="B22" t="n">
-        <v>0.597008333333333</v>
-      </c>
-      <c r="C22" t="n">
         <v>8.02634166666667</v>
       </c>
     </row>
@@ -602,9 +535,6 @@
         <v>31321</v>
       </c>
       <c r="B23" t="n">
-        <v>0.622318548387097</v>
-      </c>
-      <c r="C23" t="n">
         <v>8.22921908602151</v>
       </c>
     </row>
@@ -613,9 +543,6 @@
         <v>31352</v>
       </c>
       <c r="B24" t="n">
-        <v>0.652079276773296</v>
-      </c>
-      <c r="C24" t="n">
         <v>8.54600973574409</v>
       </c>
     </row>
@@ -624,9 +551,6 @@
         <v>31382</v>
       </c>
       <c r="B25" t="n">
-        <v>0.434021505376344</v>
-      </c>
-      <c r="C25" t="n">
         <v>6.76173924731183</v>
       </c>
     </row>
@@ -635,9 +559,6 @@
         <v>31413</v>
       </c>
       <c r="B26" t="n">
-        <v>0.470102150537634</v>
-      </c>
-      <c r="C26" t="n">
         <v>7.01869758064516</v>
       </c>
     </row>
@@ -646,9 +567,6 @@
         <v>31444</v>
       </c>
       <c r="B27" t="n">
-        <v>0.251276785714286</v>
-      </c>
-      <c r="C27" t="n">
         <v>5.20416071428571</v>
       </c>
     </row>
@@ -657,9 +575,6 @@
         <v>31472</v>
       </c>
       <c r="B28" t="n">
-        <v>0.182197580645161</v>
-      </c>
-      <c r="C28" t="n">
         <v>4.57737096774194</v>
       </c>
     </row>
@@ -668,9 +583,6 @@
         <v>31503</v>
       </c>
       <c r="B29" t="n">
-        <v>0.217911111111111</v>
-      </c>
-      <c r="C29" t="n">
         <v>4.98126666666667</v>
       </c>
     </row>
@@ -679,9 +591,6 @@
         <v>31533</v>
       </c>
       <c r="B30" t="n">
-        <v>0.397315860215054</v>
-      </c>
-      <c r="C30" t="n">
         <v>6.47003897849462</v>
       </c>
     </row>
@@ -690,9 +599,6 @@
         <v>31564</v>
       </c>
       <c r="B31" t="n">
-        <v>0.489366666666667</v>
-      </c>
-      <c r="C31" t="n">
         <v>7.12390416666667</v>
       </c>
     </row>
@@ -701,9 +607,6 @@
         <v>31594</v>
       </c>
       <c r="B32" t="n">
-        <v>0.479340053763441</v>
-      </c>
-      <c r="C32" t="n">
         <v>7.06738575268817</v>
       </c>
     </row>
@@ -712,9 +615,6 @@
         <v>31625</v>
       </c>
       <c r="B33" t="n">
-        <v>0.546586021505376</v>
-      </c>
-      <c r="C33" t="n">
         <v>7.58317069892473</v>
       </c>
     </row>
@@ -723,9 +623,6 @@
         <v>31656</v>
       </c>
       <c r="B34" t="n">
-        <v>0.699484722222222</v>
-      </c>
-      <c r="C34" t="n">
         <v>8.898025</v>
       </c>
     </row>
@@ -734,9 +631,6 @@
         <v>31686</v>
       </c>
       <c r="B35" t="n">
-        <v>0.632296096904441</v>
-      </c>
-      <c r="C35" t="n">
         <v>8.39283041722746</v>
       </c>
     </row>
@@ -745,9 +639,6 @@
         <v>31717</v>
       </c>
       <c r="B36" t="n">
-        <v>0.671479166666667</v>
-      </c>
-      <c r="C36" t="n">
         <v>8.77252638888889</v>
       </c>
     </row>
@@ -756,9 +647,6 @@
         <v>31747</v>
       </c>
       <c r="B37" t="n">
-        <v>0.606610215053763</v>
-      </c>
-      <c r="C37" t="n">
         <v>8.1092997311828</v>
       </c>
     </row>
@@ -767,9 +655,6 @@
         <v>31778</v>
       </c>
       <c r="B38" t="n">
-        <v>0.529774193548387</v>
-      </c>
-      <c r="C38" t="n">
         <v>7.48601747311828</v>
       </c>
     </row>
@@ -778,9 +663,6 @@
         <v>31809</v>
       </c>
       <c r="B39" t="n">
-        <v>0.492008928571429</v>
-      </c>
-      <c r="C39" t="n">
         <v>7.21058630952381</v>
       </c>
     </row>
@@ -789,9 +671,6 @@
         <v>31837</v>
       </c>
       <c r="B40" t="n">
-        <v>0.250548387096774</v>
-      </c>
-      <c r="C40" t="n">
         <v>5.24241129032258</v>
       </c>
     </row>
@@ -800,9 +679,6 @@
         <v>31868</v>
       </c>
       <c r="B41" t="n">
-        <v>0.3983375</v>
-      </c>
-      <c r="C41" t="n">
         <v>6.49896527777778</v>
       </c>
     </row>
@@ -811,9 +687,6 @@
         <v>31898</v>
       </c>
       <c r="B42" t="n">
-        <v>0.453823924731183</v>
-      </c>
-      <c r="C42" t="n">
         <v>6.88587634408602</v>
       </c>
     </row>
@@ -822,9 +695,6 @@
         <v>31929</v>
       </c>
       <c r="B43" t="n">
-        <v>0.486044444444444</v>
-      </c>
-      <c r="C43" t="n">
         <v>7.12091666666667</v>
       </c>
     </row>
@@ -833,9 +703,6 @@
         <v>31959</v>
       </c>
       <c r="B44" t="n">
-        <v>0.605645161290323</v>
-      </c>
-      <c r="C44" t="n">
         <v>8.02193682795699</v>
       </c>
     </row>
@@ -844,9 +711,6 @@
         <v>31990</v>
       </c>
       <c r="B45" t="n">
-        <v>0.612354838709677</v>
-      </c>
-      <c r="C45" t="n">
         <v>8.19708333333333</v>
       </c>
     </row>
@@ -855,9 +719,6 @@
         <v>32021</v>
       </c>
       <c r="B46" t="n">
-        <v>0.638904166666667</v>
-      </c>
-      <c r="C46" t="n">
         <v>8.48671805555556</v>
       </c>
     </row>
@@ -866,9 +727,6 @@
         <v>32051</v>
       </c>
       <c r="B47" t="n">
-        <v>0.630333781965007</v>
-      </c>
-      <c r="C47" t="n">
         <v>8.45529071332436</v>
       </c>
     </row>
@@ -877,9 +735,6 @@
         <v>32082</v>
       </c>
       <c r="B48" t="n">
-        <v>0.684751388888889</v>
-      </c>
-      <c r="C48" t="n">
         <v>8.85733333333333</v>
       </c>
     </row>
@@ -888,9 +743,6 @@
         <v>32112</v>
       </c>
       <c r="B49" t="n">
-        <v>0.666323924731183</v>
-      </c>
-      <c r="C49" t="n">
         <v>8.67883870967742</v>
       </c>
     </row>
@@ -899,9 +751,6 @@
         <v>32143</v>
       </c>
       <c r="B50" t="n">
-        <v>0.495362903225806</v>
-      </c>
-      <c r="C50" t="n">
         <v>7.24458198924731</v>
       </c>
     </row>
@@ -910,9 +759,6 @@
         <v>32174</v>
       </c>
       <c r="B51" t="n">
-        <v>0.436666666666667</v>
-      </c>
-      <c r="C51" t="n">
         <v>6.78926005747126</v>
       </c>
     </row>
@@ -921,9 +767,6 @@
         <v>32203</v>
       </c>
       <c r="B52" t="n">
-        <v>0.280456989247312</v>
-      </c>
-      <c r="C52" t="n">
         <v>5.55990860215054</v>
       </c>
     </row>
@@ -932,9 +775,6 @@
         <v>32234</v>
       </c>
       <c r="B53" t="n">
-        <v>0.233236111111111</v>
-      </c>
-      <c r="C53" t="n">
         <v>5.08690972222222</v>
       </c>
     </row>
@@ -943,9 +783,6 @@
         <v>32264</v>
       </c>
       <c r="B54" t="n">
-        <v>0.308702956989247</v>
-      </c>
-      <c r="C54" t="n">
         <v>5.70318010752688</v>
       </c>
     </row>
@@ -954,9 +791,6 @@
         <v>32295</v>
       </c>
       <c r="B55" t="n">
-        <v>0.472115277777778</v>
-      </c>
-      <c r="C55" t="n">
         <v>6.99625555555556</v>
       </c>
     </row>
@@ -965,9 +799,6 @@
         <v>32325</v>
       </c>
       <c r="B56" t="n">
-        <v>0.590383064516129</v>
-      </c>
-      <c r="C56" t="n">
         <v>7.9715497311828</v>
       </c>
     </row>
@@ -976,9 +807,6 @@
         <v>32356</v>
       </c>
       <c r="B57" t="n">
-        <v>0.685897849462366</v>
-      </c>
-      <c r="C57" t="n">
         <v>8.79095161290323</v>
       </c>
     </row>
@@ -987,9 +815,6 @@
         <v>32387</v>
       </c>
       <c r="B58" t="n">
-        <v>0.707441666666667</v>
-      </c>
-      <c r="C58" t="n">
         <v>9.10955277777778</v>
       </c>
     </row>
@@ -998,9 +823,6 @@
         <v>32417</v>
       </c>
       <c r="B59" t="n">
-        <v>0.669472409152086</v>
-      </c>
-      <c r="C59" t="n">
         <v>8.78322207267833</v>
       </c>
     </row>
@@ -1009,9 +831,6 @@
         <v>32448</v>
       </c>
       <c r="B60" t="n">
-        <v>0.683763888888889</v>
-      </c>
-      <c r="C60" t="n">
         <v>8.85415</v>
       </c>
     </row>
@@ -1020,9 +839,6 @@
         <v>32478</v>
       </c>
       <c r="B61" t="n">
-        <v>0.485310483870968</v>
-      </c>
-      <c r="C61" t="n">
         <v>7.14916935483871</v>
       </c>
     </row>
@@ -1031,9 +847,6 @@
         <v>32509</v>
       </c>
       <c r="B62" t="n">
-        <v>0.46154435483871</v>
-      </c>
-      <c r="C62" t="n">
         <v>6.98576478494624</v>
       </c>
     </row>
@@ -1042,9 +855,6 @@
         <v>32540</v>
       </c>
       <c r="B63" t="n">
-        <v>0.477604166666667</v>
-      </c>
-      <c r="C63" t="n">
         <v>7.09411607142857</v>
       </c>
     </row>
@@ -1053,9 +863,6 @@
         <v>32568</v>
       </c>
       <c r="B64" t="n">
-        <v>0.320815860215054</v>
-      </c>
-      <c r="C64" t="n">
         <v>5.83562231182796</v>
       </c>
     </row>
@@ -1064,9 +871,6 @@
         <v>32599</v>
       </c>
       <c r="B65" t="n">
-        <v>0.170880555555556</v>
-      </c>
-      <c r="C65" t="n">
         <v>4.59244166666667</v>
       </c>
     </row>
@@ -1075,9 +879,6 @@
         <v>32629</v>
       </c>
       <c r="B66" t="n">
-        <v>0.277834677419355</v>
-      </c>
-      <c r="C66" t="n">
         <v>5.54739516129032</v>
       </c>
     </row>
@@ -1086,9 +887,6 @@
         <v>32660</v>
       </c>
       <c r="B67" t="n">
-        <v>0.365754166666667</v>
-      </c>
-      <c r="C67" t="n">
         <v>6.20040277777778</v>
       </c>
     </row>
@@ -1097,9 +895,6 @@
         <v>32690</v>
       </c>
       <c r="B68" t="n">
-        <v>0.456729838709677</v>
-      </c>
-      <c r="C68" t="n">
         <v>6.85740591397849</v>
       </c>
     </row>
@@ -1108,9 +903,6 @@
         <v>32721</v>
       </c>
       <c r="B69" t="n">
-        <v>0.580481182795699</v>
-      </c>
-      <c r="C69" t="n">
         <v>7.83947177419355</v>
       </c>
     </row>
@@ -1119,9 +911,6 @@
         <v>32752</v>
       </c>
       <c r="B70" t="n">
-        <v>0.604670833333333</v>
-      </c>
-      <c r="C70" t="n">
         <v>8.09187916666667</v>
       </c>
     </row>
@@ -1130,9 +919,6 @@
         <v>32782</v>
       </c>
       <c r="B71" t="n">
-        <v>0.68306998654105</v>
-      </c>
-      <c r="C71" t="n">
         <v>8.89019380888291</v>
       </c>
     </row>
@@ -1141,9 +927,6 @@
         <v>32813</v>
       </c>
       <c r="B72" t="n">
-        <v>0.659391666666667</v>
-      </c>
-      <c r="C72" t="n">
         <v>8.57816388888889</v>
       </c>
     </row>
@@ -1152,9 +935,6 @@
         <v>32843</v>
       </c>
       <c r="B73" t="n">
-        <v>0.493934139784946</v>
-      </c>
-      <c r="C73" t="n">
         <v>7.19697043010753</v>
       </c>
     </row>
@@ -1163,9 +943,6 @@
         <v>32874</v>
       </c>
       <c r="B74" t="n">
-        <v>0.597676075268817</v>
-      </c>
-      <c r="C74" t="n">
         <v>7.99114784946237</v>
       </c>
     </row>
@@ -1174,9 +951,6 @@
         <v>32905</v>
       </c>
       <c r="B75" t="n">
-        <v>0.385660714285714</v>
-      </c>
-      <c r="C75" t="n">
         <v>6.40448214285714</v>
       </c>
     </row>
@@ -1185,9 +959,6 @@
         <v>32933</v>
       </c>
       <c r="B76" t="n">
-        <v>0.456041666666667</v>
-      </c>
-      <c r="C76" t="n">
         <v>6.90527956989247</v>
       </c>
     </row>
@@ -1196,9 +967,6 @@
         <v>32964</v>
       </c>
       <c r="B77" t="n">
-        <v>0.415302777777778</v>
-      </c>
-      <c r="C77" t="n">
         <v>6.61479305555556</v>
       </c>
     </row>
@@ -1207,9 +975,6 @@
         <v>32994</v>
       </c>
       <c r="B78" t="n">
-        <v>0.395111559139785</v>
-      </c>
-      <c r="C78" t="n">
         <v>6.44856720430108</v>
       </c>
     </row>
@@ -1218,9 +983,6 @@
         <v>33025</v>
       </c>
       <c r="B79" t="n">
-        <v>0.586875</v>
-      </c>
-      <c r="C79" t="n">
         <v>7.87823888888889</v>
       </c>
     </row>
@@ -1229,9 +991,6 @@
         <v>33055</v>
       </c>
       <c r="B80" t="n">
-        <v>0.526490591397849</v>
-      </c>
-      <c r="C80" t="n">
         <v>7.42988172043011</v>
       </c>
     </row>
@@ -1240,9 +999,6 @@
         <v>33086</v>
       </c>
       <c r="B81" t="n">
-        <v>0.664576612903226</v>
-      </c>
-      <c r="C81" t="n">
         <v>8.56827150537634</v>
       </c>
     </row>
@@ -1251,9 +1007,6 @@
         <v>33117</v>
       </c>
       <c r="B82" t="n">
-        <v>0.644490277777778</v>
-      </c>
-      <c r="C82" t="n">
         <v>8.47352916666667</v>
       </c>
     </row>
@@ -1262,9 +1015,6 @@
         <v>33147</v>
       </c>
       <c r="B83" t="n">
-        <v>0.687597577388964</v>
-      </c>
-      <c r="C83" t="n">
         <v>8.89395423956931</v>
       </c>
     </row>
@@ -1273,9 +1023,6 @@
         <v>33178</v>
       </c>
       <c r="B84" t="n">
-        <v>0.664031944444444</v>
-      </c>
-      <c r="C84" t="n">
         <v>8.60631666666667</v>
       </c>
     </row>
@@ -1284,9 +1031,6 @@
         <v>33208</v>
       </c>
       <c r="B85" t="n">
-        <v>0.587772849462366</v>
-      </c>
-      <c r="C85" t="n">
         <v>8.02594892473118</v>
       </c>
     </row>
@@ -1295,9 +1039,6 @@
         <v>33239</v>
       </c>
       <c r="B86" t="n">
-        <v>0.501032258064516</v>
-      </c>
-      <c r="C86" t="n">
         <v>7.29304301075269</v>
       </c>
     </row>
@@ -1306,9 +1047,6 @@
         <v>33270</v>
       </c>
       <c r="B87" t="n">
-        <v>0.410050595238095</v>
-      </c>
-      <c r="C87" t="n">
         <v>6.55519642857143</v>
       </c>
     </row>
@@ -1317,9 +1055,6 @@
         <v>33298</v>
       </c>
       <c r="B88" t="n">
-        <v>0.383375</v>
-      </c>
-      <c r="C88" t="n">
         <v>6.34998655913978</v>
       </c>
     </row>
@@ -1328,9 +1063,6 @@
         <v>33329</v>
       </c>
       <c r="B89" t="n">
-        <v>0.308036111111111</v>
-      </c>
-      <c r="C89" t="n">
         <v>5.76213055555556</v>
       </c>
     </row>
@@ -1339,9 +1071,6 @@
         <v>33359</v>
       </c>
       <c r="B90" t="n">
-        <v>0.356752688172043</v>
-      </c>
-      <c r="C90" t="n">
         <v>6.17484274193548</v>
       </c>
     </row>
@@ -1350,9 +1079,6 @@
         <v>33390</v>
       </c>
       <c r="B91" t="n">
-        <v>0.537891666666667</v>
-      </c>
-      <c r="C91" t="n">
         <v>7.5115625</v>
       </c>
     </row>
@@ -1361,9 +1087,6 @@
         <v>33420</v>
       </c>
       <c r="B92" t="n">
-        <v>0.644674731182796</v>
-      </c>
-      <c r="C92" t="n">
         <v>8.42490994623656</v>
       </c>
     </row>
@@ -1372,9 +1095,6 @@
         <v>33451</v>
       </c>
       <c r="B93" t="n">
-        <v>0.688791666666667</v>
-      </c>
-      <c r="C93" t="n">
         <v>8.80892338709677</v>
       </c>
     </row>
@@ -1383,9 +1103,6 @@
         <v>33482</v>
       </c>
       <c r="B94" t="n">
-        <v>0.668354166666667</v>
-      </c>
-      <c r="C94" t="n">
         <v>8.65047083333333</v>
       </c>
     </row>
@@ -1394,9 +1111,6 @@
         <v>33512</v>
       </c>
       <c r="B95" t="n">
-        <v>0.662853297442799</v>
-      </c>
-      <c r="C95" t="n">
         <v>8.6794266487214</v>
       </c>
     </row>
@@ -1405,9 +1119,6 @@
         <v>33543</v>
       </c>
       <c r="B96" t="n">
-        <v>0.6539125</v>
-      </c>
-      <c r="C96" t="n">
         <v>8.5282125</v>
       </c>
     </row>
@@ -1416,9 +1127,6 @@
         <v>33573</v>
       </c>
       <c r="B97" t="n">
-        <v>0.623889784946237</v>
-      </c>
-      <c r="C97" t="n">
         <v>8.27779032258064</v>
       </c>
     </row>
@@ -1427,9 +1135,6 @@
         <v>33604</v>
       </c>
       <c r="B98" t="n">
-        <v>0.515587365591398</v>
-      </c>
-      <c r="C98" t="n">
         <v>7.42132392473118</v>
       </c>
     </row>
@@ -1438,9 +1143,6 @@
         <v>33635</v>
       </c>
       <c r="B99" t="n">
-        <v>0.44535775862069</v>
-      </c>
-      <c r="C99" t="n">
         <v>6.81979166666667</v>
       </c>
     </row>
@@ -1449,9 +1151,6 @@
         <v>33664</v>
       </c>
       <c r="B100" t="n">
-        <v>0.430129032258065</v>
-      </c>
-      <c r="C100" t="n">
         <v>6.70651747311828</v>
       </c>
     </row>
@@ -1460,9 +1159,6 @@
         <v>33695</v>
       </c>
       <c r="B101" t="n">
-        <v>0.4381</v>
-      </c>
-      <c r="C101" t="n">
         <v>6.75798472222222</v>
       </c>
     </row>
@@ -1471,9 +1167,6 @@
         <v>33725</v>
       </c>
       <c r="B102" t="n">
-        <v>0.463439516129032</v>
-      </c>
-      <c r="C102" t="n">
         <v>6.97041532258064</v>
       </c>
     </row>
@@ -1482,9 +1175,6 @@
         <v>33756</v>
       </c>
       <c r="B103" t="n">
-        <v>0.569961111111111</v>
-      </c>
-      <c r="C103" t="n">
         <v>7.73373611111111</v>
       </c>
     </row>
@@ -1493,9 +1183,6 @@
         <v>33786</v>
       </c>
       <c r="B104" t="n">
-        <v>0.559423387096774</v>
-      </c>
-      <c r="C104" t="n">
         <v>7.70864516129032</v>
       </c>
     </row>
@@ -1504,9 +1191,6 @@
         <v>33817</v>
       </c>
       <c r="B105" t="n">
-        <v>0.610786290322581</v>
-      </c>
-      <c r="C105" t="n">
         <v>8.19794489247312</v>
       </c>
     </row>
@@ -1515,9 +1199,6 @@
         <v>33848</v>
       </c>
       <c r="B106" t="n">
-        <v>0.665831944444444</v>
-      </c>
-      <c r="C106" t="n">
         <v>8.69104027777778</v>
       </c>
     </row>
@@ -1526,9 +1207,6 @@
         <v>33878</v>
       </c>
       <c r="B107" t="n">
-        <v>0.687300134589502</v>
-      </c>
-      <c r="C107" t="n">
         <v>8.90142530282638</v>
       </c>
     </row>
@@ -1537,9 +1215,6 @@
         <v>33909</v>
       </c>
       <c r="B108" t="n">
-        <v>0.679920833333333</v>
-      </c>
-      <c r="C108" t="n">
         <v>8.78029861111111</v>
       </c>
     </row>
@@ -1548,9 +1223,6 @@
         <v>33939</v>
       </c>
       <c r="B109" t="n">
-        <v>0.635915322580645</v>
-      </c>
-      <c r="C109" t="n">
         <v>8.36574327956989</v>
       </c>
     </row>
@@ -1559,9 +1231,6 @@
         <v>33970</v>
       </c>
       <c r="B110" t="n">
-        <v>0.533627688172043</v>
-      </c>
-      <c r="C110" t="n">
         <v>7.52940860215054</v>
       </c>
     </row>
@@ -1570,9 +1239,6 @@
         <v>34001</v>
       </c>
       <c r="B111" t="n">
-        <v>0.520074404761905</v>
-      </c>
-      <c r="C111" t="n">
         <v>7.42901488095238</v>
       </c>
     </row>
@@ -1581,9 +1247,6 @@
         <v>34029</v>
       </c>
       <c r="B112" t="n">
-        <v>0.479931451612903</v>
-      </c>
-      <c r="C112" t="n">
         <v>7.12348924731183</v>
       </c>
     </row>
@@ -1592,9 +1255,6 @@
         <v>34060</v>
       </c>
       <c r="B113" t="n">
-        <v>0.451523611111111</v>
-      </c>
-      <c r="C113" t="n">
         <v>6.88640694444444</v>
       </c>
     </row>
@@ -1603,9 +1263,6 @@
         <v>34090</v>
       </c>
       <c r="B114" t="n">
-        <v>0.493895161290323</v>
-      </c>
-      <c r="C114" t="n">
         <v>7.16147715053763</v>
       </c>
     </row>
@@ -1614,9 +1271,6 @@
         <v>34121</v>
       </c>
       <c r="B115" t="n">
-        <v>0.571280555555556</v>
-      </c>
-      <c r="C115" t="n">
         <v>7.78761527777778</v>
       </c>
     </row>
@@ -1625,9 +1279,6 @@
         <v>34151</v>
       </c>
       <c r="B116" t="n">
-        <v>0.600551075268817</v>
-      </c>
-      <c r="C116" t="n">
         <v>8.0355752688172</v>
       </c>
     </row>
@@ -1636,9 +1287,6 @@
         <v>34182</v>
       </c>
       <c r="B117" t="n">
-        <v>0.600262096774194</v>
-      </c>
-      <c r="C117" t="n">
         <v>8.04680107526882</v>
       </c>
     </row>
@@ -1647,9 +1295,6 @@
         <v>34213</v>
       </c>
       <c r="B118" t="n">
-        <v>0.591018055555556</v>
-      </c>
-      <c r="C118" t="n">
         <v>8.03754027777778</v>
       </c>
     </row>
@@ -1658,9 +1303,6 @@
         <v>34243</v>
       </c>
       <c r="B119" t="n">
-        <v>0.683818304172275</v>
-      </c>
-      <c r="C119" t="n">
         <v>8.8738263795424</v>
       </c>
     </row>
@@ -1669,9 +1311,6 @@
         <v>34274</v>
       </c>
       <c r="B120" t="n">
-        <v>0.680811111111111</v>
-      </c>
-      <c r="C120" t="n">
         <v>8.85422916666667</v>
       </c>
     </row>
@@ -1680,9 +1319,6 @@
         <v>34304</v>
       </c>
       <c r="B121" t="n">
-        <v>0.628176075268817</v>
-      </c>
-      <c r="C121" t="n">
         <v>8.31379704301075</v>
       </c>
     </row>
@@ -1691,9 +1327,6 @@
         <v>34335</v>
       </c>
       <c r="B122" t="n">
-        <v>0.388623655913979</v>
-      </c>
-      <c r="C122" t="n">
         <v>6.40575672043011</v>
       </c>
     </row>
@@ -1702,9 +1335,6 @@
         <v>34366</v>
       </c>
       <c r="B123" t="n">
-        <v>0.37515625</v>
-      </c>
-      <c r="C123" t="n">
         <v>6.26365327380952</v>
       </c>
     </row>
@@ -1713,9 +1343,6 @@
         <v>34394</v>
       </c>
       <c r="B124" t="n">
-        <v>0.318084677419355</v>
-      </c>
-      <c r="C124" t="n">
         <v>5.93033064516129</v>
       </c>
     </row>
@@ -1724,9 +1351,6 @@
         <v>34425</v>
       </c>
       <c r="B125" t="n">
-        <v>0.2880625</v>
-      </c>
-      <c r="C125" t="n">
         <v>5.57380694444444</v>
       </c>
     </row>
@@ -1735,9 +1359,6 @@
         <v>34455</v>
       </c>
       <c r="B126" t="n">
-        <v>0.367448924731183</v>
-      </c>
-      <c r="C126" t="n">
         <v>6.25588037634409</v>
       </c>
     </row>
@@ -1746,9 +1367,6 @@
         <v>34486</v>
       </c>
       <c r="B127" t="n">
-        <v>0.396422222222222</v>
-      </c>
-      <c r="C127" t="n">
         <v>6.49093611111111</v>
       </c>
     </row>
@@ -1757,9 +1375,6 @@
         <v>34516</v>
       </c>
       <c r="B128" t="n">
-        <v>0.560524193548387</v>
-      </c>
-      <c r="C128" t="n">
         <v>7.66685349462366</v>
       </c>
     </row>
@@ -1768,9 +1383,6 @@
         <v>34547</v>
       </c>
       <c r="B129" t="n">
-        <v>0.609611559139785</v>
-      </c>
-      <c r="C129" t="n">
         <v>8.14516129032258</v>
       </c>
     </row>
@@ -1779,9 +1391,6 @@
         <v>34578</v>
       </c>
       <c r="B130" t="n">
-        <v>0.691975</v>
-      </c>
-      <c r="C130" t="n">
         <v>8.92511666666667</v>
       </c>
     </row>
@@ -1790,9 +1399,6 @@
         <v>34608</v>
       </c>
       <c r="B131" t="n">
-        <v>0.681532974427995</v>
-      </c>
-      <c r="C131" t="n">
         <v>8.90708613728129</v>
       </c>
     </row>
@@ -1801,9 +1407,6 @@
         <v>34639</v>
       </c>
       <c r="B132" t="n">
-        <v>0.666138888888889</v>
-      </c>
-      <c r="C132" t="n">
         <v>8.73807361111111</v>
       </c>
     </row>
@@ -1812,9 +1415,6 @@
         <v>34669</v>
       </c>
       <c r="B133" t="n">
-        <v>0.638793010752688</v>
-      </c>
-      <c r="C133" t="n">
         <v>8.40663575268817</v>
       </c>
     </row>
@@ -1823,9 +1423,6 @@
         <v>34700</v>
       </c>
       <c r="B134" t="n">
-        <v>0.45672311827957</v>
-      </c>
-      <c r="C134" t="n">
         <v>6.90415860215054</v>
       </c>
     </row>
@@ -1834,9 +1431,6 @@
         <v>34731</v>
       </c>
       <c r="B135" t="n">
-        <v>0.340983630952381</v>
-      </c>
-      <c r="C135" t="n">
         <v>6.05072916666667</v>
       </c>
     </row>
@@ -1845,9 +1439,6 @@
         <v>34759</v>
       </c>
       <c r="B136" t="n">
-        <v>0.341521505376344</v>
-      </c>
-      <c r="C136" t="n">
         <v>6.0427002688172</v>
       </c>
     </row>
@@ -1856,9 +1447,6 @@
         <v>34790</v>
       </c>
       <c r="B137" t="n">
-        <v>0.270933333333333</v>
-      </c>
-      <c r="C137" t="n">
         <v>5.50214583333333</v>
       </c>
     </row>
@@ -1867,9 +1455,6 @@
         <v>34820</v>
       </c>
       <c r="B138" t="n">
-        <v>0.274229838709677</v>
-      </c>
-      <c r="C138" t="n">
         <v>5.43311827956989</v>
       </c>
     </row>
@@ -1878,9 +1463,6 @@
         <v>34851</v>
       </c>
       <c r="B139" t="n">
-        <v>0.466494444444444</v>
-      </c>
-      <c r="C139" t="n">
         <v>6.97943055555556</v>
       </c>
     </row>
@@ -1889,9 +1471,6 @@
         <v>34881</v>
       </c>
       <c r="B140" t="n">
-        <v>0.595360215053763</v>
-      </c>
-      <c r="C140" t="n">
         <v>7.95315725806452</v>
       </c>
     </row>
@@ -1900,9 +1479,6 @@
         <v>34912</v>
       </c>
       <c r="B141" t="n">
-        <v>0.645420698924731</v>
-      </c>
-      <c r="C141" t="n">
         <v>8.44740188172043</v>
       </c>
     </row>
@@ -1911,9 +1487,6 @@
         <v>34943</v>
       </c>
       <c r="B142" t="n">
-        <v>0.705438888888889</v>
-      </c>
-      <c r="C142" t="n">
         <v>9.073725</v>
       </c>
     </row>
@@ -1922,9 +1495,6 @@
         <v>34973</v>
       </c>
       <c r="B143" t="n">
-        <v>0.652345895020188</v>
-      </c>
-      <c r="C143" t="n">
         <v>8.65312920592194</v>
       </c>
     </row>
@@ -1933,9 +1503,6 @@
         <v>35004</v>
       </c>
       <c r="B144" t="n">
-        <v>0.666988888888889</v>
-      </c>
-      <c r="C144" t="n">
         <v>8.67067083333333</v>
       </c>
     </row>
@@ -1944,9 +1511,6 @@
         <v>35034</v>
       </c>
       <c r="B145" t="n">
-        <v>0.581986559139785</v>
-      </c>
-      <c r="C145" t="n">
         <v>7.93294892473118</v>
       </c>
     </row>
@@ -1955,9 +1519,6 @@
         <v>35065</v>
       </c>
       <c r="B146" t="n">
-        <v>0.487123655913978</v>
-      </c>
-      <c r="C146" t="n">
         <v>7.15636693548387</v>
       </c>
     </row>
@@ -1966,9 +1527,6 @@
         <v>35096</v>
       </c>
       <c r="B147" t="n">
-        <v>0.404166666666667</v>
-      </c>
-      <c r="C147" t="n">
         <v>6.51208908045977</v>
       </c>
     </row>
@@ -1977,9 +1535,6 @@
         <v>35125</v>
       </c>
       <c r="B148" t="n">
-        <v>0.254116935483871</v>
-      </c>
-      <c r="C148" t="n">
         <v>5.36343279569892</v>
       </c>
     </row>
@@ -1988,9 +1543,6 @@
         <v>35156</v>
       </c>
       <c r="B149" t="n">
-        <v>0.216356944444444</v>
-      </c>
-      <c r="C149" t="n">
         <v>4.84763472222222</v>
       </c>
     </row>
@@ -1999,9 +1551,6 @@
         <v>35186</v>
       </c>
       <c r="B150" t="n">
-        <v>0.290241935483871</v>
-      </c>
-      <c r="C150" t="n">
         <v>5.53273924731183</v>
       </c>
     </row>
@@ -2010,9 +1559,6 @@
         <v>35217</v>
       </c>
       <c r="B151" t="n">
-        <v>0.500397222222222</v>
-      </c>
-      <c r="C151" t="n">
         <v>7.23372916666667</v>
       </c>
     </row>
@@ -2021,9 +1567,6 @@
         <v>35247</v>
       </c>
       <c r="B152" t="n">
-        <v>0.582190860215054</v>
-      </c>
-      <c r="C152" t="n">
         <v>7.85071505376344</v>
       </c>
     </row>
@@ -2032,9 +1575,6 @@
         <v>35278</v>
       </c>
       <c r="B153" t="n">
-        <v>0.642245967741935</v>
-      </c>
-      <c r="C153" t="n">
         <v>8.373625</v>
       </c>
     </row>
@@ -2043,9 +1583,6 @@
         <v>35309</v>
       </c>
       <c r="B154" t="n">
-        <v>0.706640277777778</v>
-      </c>
-      <c r="C154" t="n">
         <v>9.09169166666667</v>
       </c>
     </row>
@@ -2054,9 +1591,6 @@
         <v>35339</v>
       </c>
       <c r="B155" t="n">
-        <v>0.709173620457604</v>
-      </c>
-      <c r="C155" t="n">
         <v>9.07504172274563</v>
       </c>
     </row>
@@ -2065,9 +1599,6 @@
         <v>35370</v>
       </c>
       <c r="B156" t="n">
-        <v>0.642570833333333</v>
-      </c>
-      <c r="C156" t="n">
         <v>8.43432083333333</v>
       </c>
     </row>
@@ -2076,9 +1607,6 @@
         <v>35400</v>
       </c>
       <c r="B157" t="n">
-        <v>0.631079301075269</v>
-      </c>
-      <c r="C157" t="n">
         <v>8.3335</v>
       </c>
     </row>
@@ -2087,9 +1615,6 @@
         <v>35431</v>
       </c>
       <c r="B158" t="n">
-        <v>0.544993279569893</v>
-      </c>
-      <c r="C158" t="n">
         <v>7.58850940860215</v>
       </c>
     </row>
@@ -2098,9 +1623,6 @@
         <v>35462</v>
       </c>
       <c r="B159" t="n">
-        <v>0.528534226190476</v>
-      </c>
-      <c r="C159" t="n">
         <v>7.44936904761905</v>
       </c>
     </row>
@@ -2109,9 +1631,6 @@
         <v>35490</v>
       </c>
       <c r="B160" t="n">
-        <v>0.417907258064516</v>
-      </c>
-      <c r="C160" t="n">
         <v>6.63729435483871</v>
       </c>
     </row>
@@ -2120,9 +1639,6 @@
         <v>35521</v>
       </c>
       <c r="B161" t="n">
-        <v>0.331368055555556</v>
-      </c>
-      <c r="C161" t="n">
         <v>5.93624861111111</v>
       </c>
     </row>
@@ -2131,9 +1647,6 @@
         <v>35551</v>
       </c>
       <c r="B162" t="n">
-        <v>0.482302419354839</v>
-      </c>
-      <c r="C162" t="n">
         <v>7.11197177419355</v>
       </c>
     </row>
@@ -2142,9 +1655,6 @@
         <v>35582</v>
       </c>
       <c r="B163" t="n">
-        <v>0.509883333333333</v>
-      </c>
-      <c r="C163" t="n">
         <v>7.31400138888889</v>
       </c>
     </row>
@@ -2153,9 +1663,6 @@
         <v>35612</v>
       </c>
       <c r="B164" t="n">
-        <v>0.615184139784946</v>
-      </c>
-      <c r="C164" t="n">
         <v>8.13902284946237</v>
       </c>
     </row>
@@ -2164,9 +1671,6 @@
         <v>35643</v>
       </c>
       <c r="B165" t="n">
-        <v>0.659872311827957</v>
-      </c>
-      <c r="C165" t="n">
         <v>8.58105779569892</v>
       </c>
     </row>
@@ -2175,9 +1679,6 @@
         <v>35674</v>
       </c>
       <c r="B166" t="n">
-        <v>0.60035</v>
-      </c>
-      <c r="C166" t="n">
         <v>8.13910694444444</v>
       </c>
     </row>
@@ -2186,9 +1687,6 @@
         <v>35704</v>
       </c>
       <c r="B167" t="n">
-        <v>0.629130551816958</v>
-      </c>
-      <c r="C167" t="n">
         <v>8.36281965006729</v>
       </c>
     </row>
@@ -2197,9 +1695,6 @@
         <v>35735</v>
       </c>
       <c r="B168" t="n">
-        <v>0.624275</v>
-      </c>
-      <c r="C168" t="n">
         <v>8.30925277777778</v>
       </c>
     </row>
@@ -2208,9 +1703,6 @@
         <v>35765</v>
       </c>
       <c r="B169" t="n">
-        <v>0.553326612903226</v>
-      </c>
-      <c r="C169" t="n">
         <v>7.70541666666667</v>
       </c>
     </row>
@@ -2219,9 +1711,6 @@
         <v>35796</v>
       </c>
       <c r="B170" t="n">
-        <v>0.403408602150538</v>
-      </c>
-      <c r="C170" t="n">
         <v>6.5182002688172</v>
       </c>
     </row>
@@ -2230,9 +1719,6 @@
         <v>35827</v>
       </c>
       <c r="B171" t="n">
-        <v>0.529839285714286</v>
-      </c>
-      <c r="C171" t="n">
         <v>7.46319642857143</v>
       </c>
     </row>
@@ -2241,9 +1727,6 @@
         <v>35855</v>
       </c>
       <c r="B172" t="n">
-        <v>0.421736559139785</v>
-      </c>
-      <c r="C172" t="n">
         <v>6.65203897849462</v>
       </c>
     </row>
@@ -2252,9 +1735,6 @@
         <v>35886</v>
       </c>
       <c r="B173" t="n">
-        <v>0.479826388888889</v>
-      </c>
-      <c r="C173" t="n">
         <v>7.08098888888889</v>
       </c>
     </row>
@@ -2263,9 +1743,6 @@
         <v>35916</v>
       </c>
       <c r="B174" t="n">
-        <v>0.548572580645161</v>
-      </c>
-      <c r="C174" t="n">
         <v>7.61914247311828</v>
       </c>
     </row>
@@ -2274,9 +1751,6 @@
         <v>35947</v>
       </c>
       <c r="B175" t="n">
-        <v>0.613275</v>
-      </c>
-      <c r="C175" t="n">
         <v>8.09165972222222</v>
       </c>
     </row>
@@ -2285,9 +1759,6 @@
         <v>35977</v>
       </c>
       <c r="B176" t="n">
-        <v>0.613295698924731</v>
-      </c>
-      <c r="C176" t="n">
         <v>8.14248387096774</v>
       </c>
     </row>
@@ -2296,9 +1767,6 @@
         <v>36008</v>
       </c>
       <c r="B177" t="n">
-        <v>0.657220430107527</v>
-      </c>
-      <c r="C177" t="n">
         <v>8.59366935483871</v>
       </c>
     </row>
@@ -2307,9 +1775,6 @@
         <v>36039</v>
       </c>
       <c r="B178" t="n">
-        <v>0.654654166666667</v>
-      </c>
-      <c r="C178" t="n">
         <v>8.67277222222222</v>
       </c>
     </row>
@@ -2318,9 +1783,6 @@
         <v>36069</v>
       </c>
       <c r="B179" t="n">
-        <v>0.702484522207268</v>
-      </c>
-      <c r="C179" t="n">
         <v>9.07591520861373</v>
       </c>
     </row>
@@ -2329,9 +1791,6 @@
         <v>36100</v>
       </c>
       <c r="B180" t="n">
-        <v>0.626258333333333</v>
-      </c>
-      <c r="C180" t="n">
         <v>8.35997777777778</v>
       </c>
     </row>
@@ -2340,9 +1799,6 @@
         <v>36130</v>
       </c>
       <c r="B181" t="n">
-        <v>0.641192204301075</v>
-      </c>
-      <c r="C181" t="n">
         <v>8.49191129032258</v>
       </c>
     </row>
@@ -2351,9 +1807,6 @@
         <v>36161</v>
       </c>
       <c r="B182" t="n">
-        <v>0.492981182795699</v>
-      </c>
-      <c r="C182" t="n">
         <v>7.22030779569892</v>
       </c>
     </row>
@@ -2362,9 +1815,6 @@
         <v>36192</v>
       </c>
       <c r="B183" t="n">
-        <v>0.509959821428571</v>
-      </c>
-      <c r="C183" t="n">
         <v>7.32745089285714</v>
       </c>
     </row>
@@ -2373,9 +1823,6 @@
         <v>36220</v>
       </c>
       <c r="B184" t="n">
-        <v>0.366592741935484</v>
-      </c>
-      <c r="C184" t="n">
         <v>6.22165860215054</v>
       </c>
     </row>
@@ -2384,9 +1831,6 @@
         <v>36251</v>
       </c>
       <c r="B185" t="n">
-        <v>0.384908333333333</v>
-      </c>
-      <c r="C185" t="n">
         <v>6.36681388888889</v>
       </c>
     </row>
@@ -2395,9 +1839,6 @@
         <v>36281</v>
       </c>
       <c r="B186" t="n">
-        <v>0.33754435483871</v>
-      </c>
-      <c r="C186" t="n">
         <v>5.96443682795699</v>
       </c>
     </row>
@@ -2406,9 +1847,6 @@
         <v>36312</v>
       </c>
       <c r="B187" t="n">
-        <v>0.482025</v>
-      </c>
-      <c r="C187" t="n">
         <v>7.08721388888889</v>
       </c>
     </row>
@@ -2417,9 +1855,6 @@
         <v>36342</v>
       </c>
       <c r="B188" t="n">
-        <v>0.594350806451613</v>
-      </c>
-      <c r="C188" t="n">
         <v>8.01592741935484</v>
       </c>
     </row>
@@ -2428,9 +1863,6 @@
         <v>36373</v>
       </c>
       <c r="B189" t="n">
-        <v>0.649268817204301</v>
-      </c>
-      <c r="C189" t="n">
         <v>8.51594623655914</v>
       </c>
     </row>
@@ -2439,9 +1871,6 @@
         <v>36404</v>
       </c>
       <c r="B190" t="n">
-        <v>0.686129166666667</v>
-      </c>
-      <c r="C190" t="n">
         <v>8.89849722222222</v>
       </c>
     </row>
@@ -2450,9 +1879,6 @@
         <v>36434</v>
       </c>
       <c r="B191" t="n">
-        <v>0.6381399730821</v>
-      </c>
-      <c r="C191" t="n">
         <v>8.51278465679677</v>
       </c>
     </row>
@@ -2461,9 +1887,6 @@
         <v>36465</v>
       </c>
       <c r="B192" t="n">
-        <v>0.612827777777778</v>
-      </c>
-      <c r="C192" t="n">
         <v>8.24969166666667</v>
       </c>
     </row>
@@ -2472,9 +1895,6 @@
         <v>36495</v>
       </c>
       <c r="B193" t="n">
-        <v>0.587766129032258</v>
-      </c>
-      <c r="C193" t="n">
         <v>7.97044220430107</v>
       </c>
     </row>
@@ -2483,9 +1903,6 @@
         <v>36526</v>
       </c>
       <c r="B194" t="n">
-        <v>0.400997311827957</v>
-      </c>
-      <c r="C194" t="n">
         <v>6.52164112903226</v>
       </c>
     </row>
@@ -2494,9 +1911,6 @@
         <v>36557</v>
       </c>
       <c r="B195" t="n">
-        <v>0.310860632183908</v>
-      </c>
-      <c r="C195" t="n">
         <v>5.66882471264368</v>
       </c>
     </row>
@@ -2505,9 +1919,6 @@
         <v>36586</v>
       </c>
       <c r="B196" t="n">
-        <v>0.366891129032258</v>
-      </c>
-      <c r="C196" t="n">
         <v>6.20976209677419</v>
       </c>
     </row>
@@ -2516,9 +1927,6 @@
         <v>36617</v>
       </c>
       <c r="B197" t="n">
-        <v>0.325527777777778</v>
-      </c>
-      <c r="C197" t="n">
         <v>5.92888888888889</v>
       </c>
     </row>
@@ -2527,9 +1935,6 @@
         <v>36647</v>
       </c>
       <c r="B198" t="n">
-        <v>0.423961021505376</v>
-      </c>
-      <c r="C198" t="n">
         <v>6.65302150537634</v>
       </c>
     </row>
@@ -2538,9 +1943,6 @@
         <v>36678</v>
       </c>
       <c r="B199" t="n">
-        <v>0.4857</v>
-      </c>
-      <c r="C199" t="n">
         <v>7.14324166666667</v>
       </c>
     </row>
@@ -2549,9 +1951,6 @@
         <v>36708</v>
       </c>
       <c r="B200" t="n">
-        <v>0.551682795698925</v>
-      </c>
-      <c r="C200" t="n">
         <v>7.59658870967742</v>
       </c>
     </row>
@@ -2560,9 +1959,6 @@
         <v>36739</v>
       </c>
       <c r="B201" t="n">
-        <v>0.61057123655914</v>
-      </c>
-      <c r="C201" t="n">
         <v>8.10183870967742</v>
       </c>
     </row>
@@ -2571,9 +1967,6 @@
         <v>36770</v>
       </c>
       <c r="B202" t="n">
-        <v>0.667609722222222</v>
-      </c>
-      <c r="C202" t="n">
         <v>8.66243333333333</v>
       </c>
     </row>
@@ -2582,9 +1975,6 @@
         <v>36800</v>
       </c>
       <c r="B203" t="n">
-        <v>0.680481830417227</v>
-      </c>
-      <c r="C203" t="n">
         <v>8.80834185733513</v>
       </c>
     </row>
@@ -2593,9 +1983,6 @@
         <v>36831</v>
       </c>
       <c r="B204" t="n">
-        <v>0.636729166666667</v>
-      </c>
-      <c r="C204" t="n">
         <v>8.42020138888889</v>
       </c>
     </row>
@@ -2604,9 +1991,6 @@
         <v>36861</v>
       </c>
       <c r="B205" t="n">
-        <v>0.520572580645161</v>
-      </c>
-      <c r="C205" t="n">
         <v>7.37975403225806</v>
       </c>
     </row>
@@ -2615,9 +1999,6 @@
         <v>36892</v>
       </c>
       <c r="B206" t="n">
-        <v>0.541302419354839</v>
-      </c>
-      <c r="C206" t="n">
         <v>7.58652553763441</v>
       </c>
     </row>
@@ -2626,9 +2007,6 @@
         <v>36923</v>
       </c>
       <c r="B207" t="n">
-        <v>0.393729166666667</v>
-      </c>
-      <c r="C207" t="n">
         <v>6.46043898809524</v>
       </c>
     </row>
@@ -2637,9 +2015,6 @@
         <v>36951</v>
       </c>
       <c r="B208" t="n">
-        <v>0.308533602150538</v>
-      </c>
-      <c r="C208" t="n">
         <v>5.73303091397849</v>
       </c>
     </row>
@@ -2648,9 +2023,6 @@
         <v>36982</v>
       </c>
       <c r="B209" t="n">
-        <v>0.318773611111111</v>
-      </c>
-      <c r="C209" t="n">
         <v>5.77535138888889</v>
       </c>
     </row>
@@ -2659,9 +2031,6 @@
         <v>37012</v>
       </c>
       <c r="B210" t="n">
-        <v>0.389770161290323</v>
-      </c>
-      <c r="C210" t="n">
         <v>6.39824462365591</v>
       </c>
     </row>
@@ -2670,9 +2039,6 @@
         <v>37043</v>
       </c>
       <c r="B211" t="n">
-        <v>0.488173611111111</v>
-      </c>
-      <c r="C211" t="n">
         <v>7.14151944444444</v>
       </c>
     </row>
@@ -2681,9 +2047,6 @@
         <v>37073</v>
       </c>
       <c r="B212" t="n">
-        <v>0.593295698924731</v>
-      </c>
-      <c r="C212" t="n">
         <v>7.95020564516129</v>
       </c>
     </row>
@@ -2692,9 +2055,6 @@
         <v>37104</v>
       </c>
       <c r="B213" t="n">
-        <v>0.706899193548387</v>
-      </c>
-      <c r="C213" t="n">
         <v>8.93502419354839</v>
       </c>
     </row>
@@ -2703,9 +2063,6 @@
         <v>37135</v>
       </c>
       <c r="B214" t="n">
-        <v>0.625048611111111</v>
-      </c>
-      <c r="C214" t="n">
         <v>8.31579861111111</v>
       </c>
     </row>
@@ -2714,9 +2071,6 @@
         <v>37165</v>
       </c>
       <c r="B215" t="n">
-        <v>0.599760430686406</v>
-      </c>
-      <c r="C215" t="n">
         <v>8.07081157469717</v>
       </c>
     </row>
@@ -2725,9 +2079,6 @@
         <v>37196</v>
       </c>
       <c r="B216" t="n">
-        <v>0.624130555555556</v>
-      </c>
-      <c r="C216" t="n">
         <v>8.36026666666667</v>
       </c>
     </row>
@@ -2736,9 +2087,6 @@
         <v>37226</v>
       </c>
       <c r="B217" t="n">
-        <v>0.696096774193548</v>
-      </c>
-      <c r="C217" t="n">
         <v>8.8513252688172</v>
       </c>
     </row>
@@ -2747,9 +2095,6 @@
         <v>37257</v>
       </c>
       <c r="B218" t="n">
-        <v>0.343282258064516</v>
-      </c>
-      <c r="C218" t="n">
         <v>6.06098252688172</v>
       </c>
     </row>
@@ -2758,9 +2103,6 @@
         <v>37288</v>
       </c>
       <c r="B219" t="n">
-        <v>0.394747023809524</v>
-      </c>
-      <c r="C219" t="n">
         <v>6.47676488095238</v>
       </c>
     </row>
@@ -2769,9 +2111,6 @@
         <v>37316</v>
       </c>
       <c r="B220" t="n">
-        <v>0.332213709677419</v>
-      </c>
-      <c r="C220" t="n">
         <v>5.9491935483871</v>
       </c>
     </row>
@@ -2780,9 +2119,6 @@
         <v>37347</v>
       </c>
       <c r="B221" t="n">
-        <v>0.286997222222222</v>
-      </c>
-      <c r="C221" t="n">
         <v>5.44576388888889</v>
       </c>
     </row>
@@ -2791,9 +2127,6 @@
         <v>37377</v>
       </c>
       <c r="B222" t="n">
-        <v>0.375297043010753</v>
-      </c>
-      <c r="C222" t="n">
         <v>6.23477956989247</v>
       </c>
     </row>
@@ -2802,9 +2135,6 @@
         <v>37408</v>
       </c>
       <c r="B223" t="n">
-        <v>0.483184722222222</v>
-      </c>
-      <c r="C223" t="n">
         <v>7.09605833333333</v>
       </c>
     </row>
@@ -2813,9 +2143,6 @@
         <v>37438</v>
       </c>
       <c r="B224" t="n">
-        <v>0.534764784946237</v>
-      </c>
-      <c r="C224" t="n">
         <v>7.49228494623656</v>
       </c>
     </row>
@@ -2824,9 +2151,6 @@
         <v>37469</v>
       </c>
       <c r="B225" t="n">
-        <v>0.679647849462366</v>
-      </c>
-      <c r="C225" t="n">
         <v>8.75802688172043</v>
       </c>
     </row>
@@ -2835,9 +2159,6 @@
         <v>37500</v>
       </c>
       <c r="B226" t="n">
-        <v>0.611241666666667</v>
-      </c>
-      <c r="C226" t="n">
         <v>8.25490972222222</v>
       </c>
     </row>
@@ -2846,9 +2167,6 @@
         <v>37530</v>
       </c>
       <c r="B227" t="n">
-        <v>0.708541666666667</v>
-      </c>
-      <c r="C227" t="n">
         <v>9.15878225806452</v>
       </c>
     </row>
@@ -2857,9 +2175,6 @@
         <v>37561</v>
       </c>
       <c r="B228" t="n">
-        <v>0.649205841446453</v>
-      </c>
-      <c r="C228" t="n">
         <v>8.56249235048679</v>
       </c>
     </row>
@@ -2868,9 +2183,6 @@
         <v>37591</v>
       </c>
       <c r="B229" t="n">
-        <v>0.583809139784946</v>
-      </c>
-      <c r="C229" t="n">
         <v>7.96014247311828</v>
       </c>
     </row>
@@ -2879,9 +2191,6 @@
         <v>37622</v>
       </c>
       <c r="B230" t="n">
-        <v>0.42092876344086</v>
-      </c>
-      <c r="C230" t="n">
         <v>6.7032123655914</v>
       </c>
     </row>
@@ -2890,9 +2199,6 @@
         <v>37653</v>
       </c>
       <c r="B231" t="n">
-        <v>0.369321428571429</v>
-      </c>
-      <c r="C231" t="n">
         <v>6.24960863095238</v>
       </c>
     </row>
@@ -2901,9 +2207,6 @@
         <v>37681</v>
       </c>
       <c r="B232" t="n">
-        <v>0.298005376344086</v>
-      </c>
-      <c r="C232" t="n">
         <v>5.66209408602151</v>
       </c>
     </row>
@@ -2912,9 +2215,6 @@
         <v>37712</v>
       </c>
       <c r="B233" t="n">
-        <v>0.300556944444444</v>
-      </c>
-      <c r="C233" t="n">
         <v>5.690075</v>
       </c>
     </row>
@@ -2923,9 +2223,6 @@
         <v>37742</v>
       </c>
       <c r="B234" t="n">
-        <v>0.373208333333333</v>
-      </c>
-      <c r="C234" t="n">
         <v>6.26990860215054</v>
       </c>
     </row>
@@ -2934,9 +2231,6 @@
         <v>37773</v>
       </c>
       <c r="B235" t="n">
-        <v>0.466636111111111</v>
-      </c>
-      <c r="C235" t="n">
         <v>6.97985</v>
       </c>
     </row>
@@ -2945,9 +2239,6 @@
         <v>37803</v>
       </c>
       <c r="B236" t="n">
-        <v>0.640018817204301</v>
-      </c>
-      <c r="C236" t="n">
         <v>8.34936155913979</v>
       </c>
     </row>
@@ -2956,9 +2247,6 @@
         <v>37834</v>
       </c>
       <c r="B237" t="n">
-        <v>0.600692204301075</v>
-      </c>
-      <c r="C237" t="n">
         <v>8.04599193548387</v>
       </c>
     </row>
@@ -2967,9 +2255,6 @@
         <v>37865</v>
       </c>
       <c r="B238" t="n">
-        <v>0.687218055555556</v>
-      </c>
-      <c r="C238" t="n">
         <v>8.86959166666667</v>
       </c>
     </row>
@@ -2978,9 +2263,6 @@
         <v>37895</v>
       </c>
       <c r="B239" t="n">
-        <v>0.671045760430686</v>
-      </c>
-      <c r="C239" t="n">
         <v>8.76052759084791</v>
       </c>
     </row>
@@ -2989,9 +2271,6 @@
         <v>37926</v>
       </c>
       <c r="B240" t="n">
-        <v>0.636618055555556</v>
-      </c>
-      <c r="C240" t="n">
         <v>8.47785</v>
       </c>
     </row>
@@ -3000,9 +2279,6 @@
         <v>37956</v>
       </c>
       <c r="B241" t="n">
-        <v>0.615470430107527</v>
-      </c>
-      <c r="C241" t="n">
         <v>8.2114435483871</v>
       </c>
     </row>
@@ -3011,9 +2287,6 @@
         <v>37987</v>
       </c>
       <c r="B242" t="n">
-        <v>0.357786290322581</v>
-      </c>
-      <c r="C242" t="n">
         <v>6.13998924731183</v>
       </c>
     </row>
@@ -3022,9 +2295,6 @@
         <v>38018</v>
       </c>
       <c r="B243" t="n">
-        <v>0.333198275862069</v>
-      </c>
-      <c r="C243" t="n">
         <v>5.97767959770115</v>
       </c>
     </row>
@@ -3033,9 +2303,6 @@
         <v>38047</v>
       </c>
       <c r="B244" t="n">
-        <v>0.407659946236559</v>
-      </c>
-      <c r="C244" t="n">
         <v>6.54418548387097</v>
       </c>
     </row>
@@ -3044,9 +2311,6 @@
         <v>38078</v>
       </c>
       <c r="B245" t="n">
-        <v>0.368068055555556</v>
-      </c>
-      <c r="C245" t="n">
         <v>6.25894444444444</v>
       </c>
     </row>
@@ -3055,9 +2319,6 @@
         <v>38108</v>
       </c>
       <c r="B246" t="n">
-        <v>0.419637096774194</v>
-      </c>
-      <c r="C246" t="n">
         <v>6.64379569892473</v>
       </c>
     </row>
@@ -3066,9 +2327,6 @@
         <v>38139</v>
       </c>
       <c r="B247" t="n">
-        <v>0.477920833333333</v>
-      </c>
-      <c r="C247" t="n">
         <v>7.09463611111111</v>
       </c>
     </row>
@@ -3077,9 +2335,6 @@
         <v>38169</v>
       </c>
       <c r="B248" t="n">
-        <v>0.507006720430108</v>
-      </c>
-      <c r="C248" t="n">
         <v>7.30401344086022</v>
       </c>
     </row>
@@ -3088,9 +2343,6 @@
         <v>38200</v>
       </c>
       <c r="B249" t="n">
-        <v>0.626424731182796</v>
-      </c>
-      <c r="C249" t="n">
         <v>8.21849193548387</v>
       </c>
     </row>
@@ -3099,9 +2351,6 @@
         <v>38231</v>
       </c>
       <c r="B250" t="n">
-        <v>0.7158</v>
-      </c>
-      <c r="C250" t="n">
         <v>9.14538611111111</v>
       </c>
     </row>
@@ -3110,9 +2359,6 @@
         <v>38261</v>
       </c>
       <c r="B251" t="n">
-        <v>0.669692204301075</v>
-      </c>
-      <c r="C251" t="n">
         <v>8.79242204301075</v>
       </c>
     </row>
@@ -3121,9 +2367,6 @@
         <v>38292</v>
       </c>
       <c r="B252" t="n">
-        <v>0.671853963838665</v>
-      </c>
-      <c r="C252" t="n">
         <v>8.72865924895688</v>
       </c>
     </row>
@@ -3132,9 +2375,6 @@
         <v>38322</v>
       </c>
       <c r="B253" t="n">
-        <v>0.595747311827957</v>
-      </c>
-      <c r="C253" t="n">
         <v>8.08158602150538</v>
       </c>
     </row>
@@ -3143,9 +2383,6 @@
         <v>38353</v>
       </c>
       <c r="B254" t="n">
-        <v>0.484557795698925</v>
-      </c>
-      <c r="C254" t="n">
         <v>7.18234274193548</v>
       </c>
     </row>
@@ -3154,9 +2391,6 @@
         <v>38384</v>
       </c>
       <c r="B255" t="n">
-        <v>0.455052083333333</v>
-      </c>
-      <c r="C255" t="n">
         <v>6.91628720238095</v>
       </c>
     </row>
@@ -3165,9 +2399,6 @@
         <v>38412</v>
       </c>
       <c r="B256" t="n">
-        <v>0.356032258064516</v>
-      </c>
-      <c r="C256" t="n">
         <v>6.10139516129032</v>
       </c>
     </row>
@@ -3176,9 +2407,6 @@
         <v>38443</v>
       </c>
       <c r="B257" t="n">
-        <v>0.407709722222222</v>
-      </c>
-      <c r="C257" t="n">
         <v>6.53547638888889</v>
       </c>
     </row>
@@ -3187,9 +2415,6 @@
         <v>38473</v>
       </c>
       <c r="B258" t="n">
-        <v>0.424629032258065</v>
-      </c>
-      <c r="C258" t="n">
         <v>6.64344220430108</v>
       </c>
     </row>
@@ -3198,9 +2423,6 @@
         <v>38504</v>
       </c>
       <c r="B259" t="n">
-        <v>0.49725</v>
-      </c>
-      <c r="C259" t="n">
         <v>7.19025972222222</v>
       </c>
     </row>
@@ -3209,9 +2431,6 @@
         <v>38534</v>
       </c>
       <c r="B260" t="n">
-        <v>0.573622311827957</v>
-      </c>
-      <c r="C260" t="n">
         <v>7.76842741935484</v>
       </c>
     </row>
@@ -3220,9 +2439,6 @@
         <v>38565</v>
       </c>
       <c r="B261" t="n">
-        <v>0.674811827956989</v>
-      </c>
-      <c r="C261" t="n">
         <v>8.66224327956989</v>
       </c>
     </row>
@@ -3231,9 +2447,6 @@
         <v>38596</v>
       </c>
       <c r="B262" t="n">
-        <v>0.670377777777778</v>
-      </c>
-      <c r="C262" t="n">
         <v>8.67760694444445</v>
       </c>
     </row>
@@ -3242,9 +2455,6 @@
         <v>38626</v>
       </c>
       <c r="B263" t="n">
-        <v>0.691944818304172</v>
-      </c>
-      <c r="C263" t="n">
         <v>8.99129071332436</v>
       </c>
     </row>
@@ -3253,9 +2463,6 @@
         <v>38657</v>
       </c>
       <c r="B264" t="n">
-        <v>0.68155</v>
-      </c>
-      <c r="C264" t="n">
         <v>8.79805</v>
       </c>
     </row>
@@ -3264,9 +2471,6 @@
         <v>38687</v>
       </c>
       <c r="B265" t="n">
-        <v>0.595120967741935</v>
-      </c>
-      <c r="C265" t="n">
         <v>7.96993279569892</v>
       </c>
     </row>
@@ -3275,9 +2479,6 @@
         <v>38718</v>
       </c>
       <c r="B266" t="n">
-        <v>0.593807795698925</v>
-      </c>
-      <c r="C266" t="n">
         <v>7.9928185483871</v>
       </c>
     </row>
@@ -3286,9 +2487,6 @@
         <v>38749</v>
       </c>
       <c r="B267" t="n">
-        <v>0.373477678571429</v>
-      </c>
-      <c r="C267" t="n">
         <v>6.31361755952381</v>
       </c>
     </row>
@@ -3297,9 +2495,6 @@
         <v>38777</v>
       </c>
       <c r="B268" t="n">
-        <v>0.330034946236559</v>
-      </c>
-      <c r="C268" t="n">
         <v>6.00809543010753</v>
       </c>
     </row>
@@ -3308,9 +2503,6 @@
         <v>38808</v>
       </c>
       <c r="B269" t="n">
-        <v>0.217598611111111</v>
-      </c>
-      <c r="C269" t="n">
         <v>4.91858888888889</v>
       </c>
     </row>
@@ -3319,9 +2511,6 @@
         <v>38838</v>
       </c>
       <c r="B270" t="n">
-        <v>0.311733870967742</v>
-      </c>
-      <c r="C270" t="n">
         <v>5.78735215053763</v>
       </c>
     </row>
@@ -3330,9 +2519,6 @@
         <v>38869</v>
       </c>
       <c r="B271" t="n">
-        <v>0.511252777777778</v>
-      </c>
-      <c r="C271" t="n">
         <v>7.258075</v>
       </c>
     </row>
@@ -3341,9 +2527,6 @@
         <v>38899</v>
       </c>
       <c r="B272" t="n">
-        <v>0.521212365591398</v>
-      </c>
-      <c r="C272" t="n">
         <v>7.37900806451613</v>
       </c>
     </row>
@@ -3352,9 +2535,6 @@
         <v>38930</v>
       </c>
       <c r="B273" t="n">
-        <v>0.589127688172043</v>
-      </c>
-      <c r="C273" t="n">
         <v>7.94373387096774</v>
       </c>
     </row>
@@ -3363,9 +2543,6 @@
         <v>38961</v>
       </c>
       <c r="B274" t="n">
-        <v>0.635295833333333</v>
-      </c>
-      <c r="C274" t="n">
         <v>8.36359027777778</v>
       </c>
     </row>
@@ -3374,9 +2551,6 @@
         <v>38991</v>
       </c>
       <c r="B275" t="n">
-        <v>0.669217741935484</v>
-      </c>
-      <c r="C275" t="n">
         <v>8.67330241935484</v>
       </c>
     </row>
@@ -3385,9 +2559,6 @@
         <v>39022</v>
       </c>
       <c r="B276" t="n">
-        <v>0.638933240611961</v>
-      </c>
-      <c r="C276" t="n">
         <v>8.42099026425591</v>
       </c>
     </row>
@@ -3396,9 +2567,6 @@
         <v>39052</v>
       </c>
       <c r="B277" t="n">
-        <v>0.584329301075269</v>
-      </c>
-      <c r="C277" t="n">
         <v>7.93563306451613</v>
       </c>
     </row>
@@ -3407,9 +2575,6 @@
         <v>39083</v>
       </c>
       <c r="B278" t="n">
-        <v>0.552731182795699</v>
-      </c>
-      <c r="C278" t="n">
         <v>7.6519126344086</v>
       </c>
     </row>
@@ -3418,9 +2583,6 @@
         <v>39114</v>
       </c>
       <c r="B279" t="n">
-        <v>0.339438988095238</v>
-      </c>
-      <c r="C279" t="n">
         <v>5.98907142857143</v>
       </c>
     </row>
@@ -3429,9 +2591,6 @@
         <v>39142</v>
       </c>
       <c r="B280" t="n">
-        <v>0.384434139784946</v>
-      </c>
-      <c r="C280" t="n">
         <v>6.36266397849462</v>
       </c>
     </row>
@@ -3440,9 +2599,6 @@
         <v>39173</v>
       </c>
       <c r="B281" t="n">
-        <v>0.305873611111111</v>
-      </c>
-      <c r="C281" t="n">
         <v>5.73310694444444</v>
       </c>
     </row>
@@ -3451,9 +2607,6 @@
         <v>39203</v>
       </c>
       <c r="B282" t="n">
-        <v>0.408958333333333</v>
-      </c>
-      <c r="C282" t="n">
         <v>6.5369126344086</v>
       </c>
     </row>
@@ -3462,9 +2615,6 @@
         <v>39234</v>
       </c>
       <c r="B283" t="n">
-        <v>0.563177777777778</v>
-      </c>
-      <c r="C283" t="n">
         <v>7.71215972222222</v>
       </c>
     </row>
@@ -3473,9 +2623,6 @@
         <v>39264</v>
       </c>
       <c r="B284" t="n">
-        <v>0.593235215053763</v>
-      </c>
-      <c r="C284" t="n">
         <v>7.95753897849462</v>
       </c>
     </row>
@@ -3484,9 +2631,6 @@
         <v>39295</v>
       </c>
       <c r="B285" t="n">
-        <v>0.736442204301075</v>
-      </c>
-      <c r="C285" t="n">
         <v>9.22485080645161</v>
       </c>
     </row>
@@ -3495,9 +2639,6 @@
         <v>39326</v>
       </c>
       <c r="B286" t="n">
-        <v>0.757652777777778</v>
-      </c>
-      <c r="C286" t="n">
         <v>9.50251111111111</v>
       </c>
     </row>
@@ -3506,9 +2647,6 @@
         <v>39356</v>
       </c>
       <c r="B287" t="n">
-        <v>0.714511440107672</v>
-      </c>
-      <c r="C287" t="n">
         <v>9.17639838492598</v>
       </c>
     </row>
@@ -3517,9 +2655,6 @@
         <v>39387</v>
       </c>
       <c r="B288" t="n">
-        <v>0.662501388888889</v>
-      </c>
-      <c r="C288" t="n">
         <v>8.6857625</v>
       </c>
     </row>
@@ -3528,9 +2663,6 @@
         <v>39417</v>
       </c>
       <c r="B289" t="n">
-        <v>0.599979838709677</v>
-      </c>
-      <c r="C289" t="n">
         <v>8.06690188172043</v>
       </c>
     </row>
@@ -3539,9 +2671,6 @@
         <v>39448</v>
       </c>
       <c r="B290" t="n">
-        <v>0.47204435483871</v>
-      </c>
-      <c r="C290" t="n">
         <v>7.05694489247312</v>
       </c>
     </row>
@@ -3550,9 +2679,6 @@
         <v>39479</v>
       </c>
       <c r="B291" t="n">
-        <v>0.41014224137931</v>
-      </c>
-      <c r="C291" t="n">
         <v>6.56733333333333</v>
       </c>
     </row>
@@ -3561,9 +2687,6 @@
         <v>39508</v>
       </c>
       <c r="B292" t="n">
-        <v>0.198655913978495</v>
-      </c>
-      <c r="C292" t="n">
         <v>4.70241935483871</v>
       </c>
     </row>
@@ -3572,9 +2695,6 @@
         <v>39539</v>
       </c>
       <c r="B293" t="n">
-        <v>0.254486111111111</v>
-      </c>
-      <c r="C293" t="n">
         <v>5.30139722222222</v>
       </c>
     </row>
@@ -3583,9 +2703,6 @@
         <v>39569</v>
       </c>
       <c r="B294" t="n">
-        <v>0.287116935483871</v>
-      </c>
-      <c r="C294" t="n">
         <v>5.46688575268817</v>
       </c>
     </row>
@@ -3594,9 +2711,6 @@
         <v>39600</v>
       </c>
       <c r="B295" t="n">
-        <v>0.449355555555556</v>
-      </c>
-      <c r="C295" t="n">
         <v>6.80836666666667</v>
       </c>
     </row>
@@ -3605,9 +2719,6 @@
         <v>39630</v>
       </c>
       <c r="B296" t="n">
-        <v>0.571954301075269</v>
-      </c>
-      <c r="C296" t="n">
         <v>7.75515591397849</v>
       </c>
     </row>
@@ -3616,9 +2727,6 @@
         <v>39661</v>
       </c>
       <c r="B297" t="n">
-        <v>0.541427419354839</v>
-      </c>
-      <c r="C297" t="n">
         <v>7.55284677419355</v>
       </c>
     </row>
@@ -3627,9 +2735,6 @@
         <v>39692</v>
       </c>
       <c r="B298" t="n">
-        <v>0.646980555555556</v>
-      </c>
-      <c r="C298" t="n">
         <v>8.40021666666667</v>
       </c>
     </row>
@@ -3638,9 +2743,6 @@
         <v>39722</v>
       </c>
       <c r="B299" t="n">
-        <v>0.721168236877524</v>
-      </c>
-      <c r="C299" t="n">
         <v>9.22221534320323</v>
       </c>
     </row>
@@ -3649,9 +2751,6 @@
         <v>39753</v>
       </c>
       <c r="B300" t="n">
-        <v>0.673426388888889</v>
-      </c>
-      <c r="C300" t="n">
         <v>8.67572222222222</v>
       </c>
     </row>
@@ -3660,9 +2759,6 @@
         <v>39783</v>
       </c>
       <c r="B301" t="n">
-        <v>0.565099462365591</v>
-      </c>
-      <c r="C301" t="n">
         <v>7.78804032258065</v>
       </c>
     </row>
@@ -3671,9 +2767,6 @@
         <v>39814</v>
       </c>
       <c r="B302" t="n">
-        <v>0.45367876344086</v>
-      </c>
-      <c r="C302" t="n">
         <v>6.92436155913979</v>
       </c>
     </row>
@@ -3682,9 +2775,6 @@
         <v>39845</v>
       </c>
       <c r="B303" t="n">
-        <v>0.324702380952381</v>
-      </c>
-      <c r="C303" t="n">
         <v>5.92039136904762</v>
       </c>
     </row>
@@ -3693,9 +2783,6 @@
         <v>39873</v>
       </c>
       <c r="B304" t="n">
-        <v>0.277008064516129</v>
-      </c>
-      <c r="C304" t="n">
         <v>5.56788172043011</v>
       </c>
     </row>
@@ -3704,9 +2791,6 @@
         <v>39904</v>
       </c>
       <c r="B305" t="n">
-        <v>0.175302777777778</v>
-      </c>
-      <c r="C305" t="n">
         <v>4.51647083333333</v>
       </c>
     </row>
@@ -3715,9 +2799,6 @@
         <v>39934</v>
       </c>
       <c r="B306" t="n">
-        <v>0.180384408602151</v>
-      </c>
-      <c r="C306" t="n">
         <v>4.47817338709677</v>
       </c>
     </row>
@@ -3726,9 +2807,6 @@
         <v>39965</v>
       </c>
       <c r="B307" t="n">
-        <v>0.371641666666667</v>
-      </c>
-      <c r="C307" t="n">
         <v>6.22025833333333</v>
       </c>
     </row>
@@ -3737,9 +2815,6 @@
         <v>39995</v>
       </c>
       <c r="B308" t="n">
-        <v>0.440272849462366</v>
-      </c>
-      <c r="C308" t="n">
         <v>6.73998252688172</v>
       </c>
     </row>
@@ -3748,9 +2823,6 @@
         <v>40026</v>
       </c>
       <c r="B309" t="n">
-        <v>0.558708333333333</v>
-      </c>
-      <c r="C309" t="n">
         <v>7.66108870967742</v>
       </c>
     </row>
@@ -3759,9 +2831,6 @@
         <v>40057</v>
       </c>
       <c r="B310" t="n">
-        <v>0.603508333333333</v>
-      </c>
-      <c r="C310" t="n">
         <v>8.02434166666667</v>
       </c>
     </row>
@@ -3770,9 +2839,6 @@
         <v>40087</v>
       </c>
       <c r="B311" t="n">
-        <v>0.586806191117093</v>
-      </c>
-      <c r="C311" t="n">
         <v>7.95002153432032</v>
       </c>
     </row>
@@ -3781,9 +2847,6 @@
         <v>40118</v>
       </c>
       <c r="B312" t="n">
-        <v>0.675098611111111</v>
-      </c>
-      <c r="C312" t="n">
         <v>8.73514722222222</v>
       </c>
     </row>
@@ -3792,9 +2855,6 @@
         <v>40148</v>
       </c>
       <c r="B313" t="n">
-        <v>0.558420698924731</v>
-      </c>
-      <c r="C313" t="n">
         <v>7.71706720430107</v>
       </c>
     </row>
@@ -3803,9 +2863,6 @@
         <v>40179</v>
       </c>
       <c r="B314" t="n">
-        <v>0.395971774193548</v>
-      </c>
-      <c r="C314" t="n">
         <v>6.46645430107527</v>
       </c>
     </row>
@@ -3814,9 +2871,6 @@
         <v>40210</v>
       </c>
       <c r="B315" t="n">
-        <v>0.468169642857143</v>
-      </c>
-      <c r="C315" t="n">
         <v>7.00763988095238</v>
       </c>
     </row>
@@ -3825,9 +2879,6 @@
         <v>40238</v>
       </c>
       <c r="B316" t="n">
-        <v>0.39154435483871</v>
-      </c>
-      <c r="C316" t="n">
         <v>6.43036693548387</v>
       </c>
     </row>
@@ -3836,9 +2887,6 @@
         <v>40269</v>
       </c>
       <c r="B317" t="n">
-        <v>0.357147222222222</v>
-      </c>
-      <c r="C317" t="n">
         <v>6.12113472222222</v>
       </c>
     </row>
@@ -3847,9 +2895,6 @@
         <v>40299</v>
       </c>
       <c r="B318" t="n">
-        <v>0.370911290322581</v>
-      </c>
-      <c r="C318" t="n">
         <v>6.23377553763441</v>
       </c>
     </row>
@@ -3858,9 +2903,6 @@
         <v>40330</v>
       </c>
       <c r="B319" t="n">
-        <v>0.487511111111111</v>
-      </c>
-      <c r="C319" t="n">
         <v>7.09181805555556</v>
       </c>
     </row>
@@ -3869,9 +2911,6 @@
         <v>40360</v>
       </c>
       <c r="B320" t="n">
-        <v>0.589969086021505</v>
-      </c>
-      <c r="C320" t="n">
         <v>7.9127311827957</v>
       </c>
     </row>
@@ -3880,9 +2919,6 @@
         <v>40391</v>
       </c>
       <c r="B321" t="n">
-        <v>0.670938172043011</v>
-      </c>
-      <c r="C321" t="n">
         <v>8.63809274193548</v>
       </c>
     </row>
@@ -3891,9 +2927,6 @@
         <v>40422</v>
       </c>
       <c r="B322" t="n">
-        <v>0.700094444444444</v>
-      </c>
-      <c r="C322" t="n">
         <v>8.91371805555556</v>
       </c>
     </row>
@@ -3902,9 +2935,6 @@
         <v>40452</v>
       </c>
       <c r="B323" t="n">
-        <v>0.551794078061911</v>
-      </c>
-      <c r="C323" t="n">
         <v>7.71204710632571</v>
       </c>
     </row>
@@ -3913,9 +2943,6 @@
         <v>40483</v>
       </c>
       <c r="B324" t="n">
-        <v>0.625091666666667</v>
-      </c>
-      <c r="C324" t="n">
         <v>8.35835555555555</v>
       </c>
     </row>
@@ -3924,9 +2951,6 @@
         <v>40513</v>
       </c>
       <c r="B325" t="n">
-        <v>0.490322580645161</v>
-      </c>
-      <c r="C325" t="n">
         <v>7.20294758064516</v>
       </c>
     </row>
@@ -3935,9 +2959,6 @@
         <v>40544</v>
       </c>
       <c r="B326" t="n">
-        <v>0.351213709677419</v>
-      </c>
-      <c r="C326" t="n">
         <v>6.07039919354839</v>
       </c>
     </row>
@@ -3946,9 +2967,6 @@
         <v>40575</v>
       </c>
       <c r="B327" t="n">
-        <v>0.341583333333333</v>
-      </c>
-      <c r="C327" t="n">
         <v>6.01066517857143</v>
       </c>
     </row>
@@ -3957,9 +2975,6 @@
         <v>40603</v>
       </c>
       <c r="B328" t="n">
-        <v>0.288286290322581</v>
-      </c>
-      <c r="C328" t="n">
         <v>5.62534408602151</v>
       </c>
     </row>
@@ -3968,9 +2983,6 @@
         <v>40634</v>
       </c>
       <c r="B329" t="n">
-        <v>0.259354166666667</v>
-      </c>
-      <c r="C329" t="n">
         <v>5.29541111111111</v>
       </c>
     </row>
@@ -3979,9 +2991,6 @@
         <v>40664</v>
       </c>
       <c r="B330" t="n">
-        <v>0.352331989247312</v>
-      </c>
-      <c r="C330" t="n">
         <v>6.01846370967742</v>
       </c>
     </row>
@@ -3990,9 +2999,6 @@
         <v>40695</v>
       </c>
       <c r="B331" t="n">
-        <v>0.429723611111111</v>
-      </c>
-      <c r="C331" t="n">
         <v>6.68794444444444</v>
       </c>
     </row>
@@ -4001,9 +3007,6 @@
         <v>40725</v>
       </c>
       <c r="B332" t="n">
-        <v>0.511506720430107</v>
-      </c>
-      <c r="C332" t="n">
         <v>7.3145188172043</v>
       </c>
     </row>
@@ -4012,9 +3015,6 @@
         <v>40756</v>
       </c>
       <c r="B333" t="n">
-        <v>0.603173387096774</v>
-      </c>
-      <c r="C333" t="n">
         <v>8.02273655913979</v>
       </c>
     </row>
@@ -4023,9 +3023,6 @@
         <v>40787</v>
       </c>
       <c r="B334" t="n">
-        <v>0.734481944444444</v>
-      </c>
-      <c r="C334" t="n">
         <v>9.28046388888889</v>
       </c>
     </row>
@@ -4034,9 +3031,6 @@
         <v>40817</v>
       </c>
       <c r="B335" t="n">
-        <v>0.59278331090175</v>
-      </c>
-      <c r="C335" t="n">
         <v>8.03815881561238</v>
       </c>
     </row>
@@ -4045,9 +3039,6 @@
         <v>40848</v>
       </c>
       <c r="B336" t="n">
-        <v>0.660627777777778</v>
-      </c>
-      <c r="C336" t="n">
         <v>8.55243611111111</v>
       </c>
     </row>
@@ -4056,9 +3047,6 @@
         <v>40878</v>
       </c>
       <c r="B337" t="n">
-        <v>0.649172043010753</v>
-      </c>
-      <c r="C337" t="n">
         <v>8.46814247311828</v>
       </c>
     </row>
@@ -4067,9 +3055,6 @@
         <v>40909</v>
       </c>
       <c r="B338" t="n">
-        <v>0.562248655913979</v>
-      </c>
-      <c r="C338" t="n">
         <v>7.77748252688172</v>
       </c>
     </row>
@@ -4078,9 +3063,6 @@
         <v>40940</v>
       </c>
       <c r="B339" t="n">
-        <v>0.468396551724138</v>
-      </c>
-      <c r="C339" t="n">
         <v>7.02929597701149</v>
       </c>
     </row>
@@ -4089,9 +3071,6 @@
         <v>40969</v>
       </c>
       <c r="B340" t="n">
-        <v>0.441102150537634</v>
-      </c>
-      <c r="C340" t="n">
         <v>6.79436290322581</v>
       </c>
     </row>
@@ -4100,9 +3079,6 @@
         <v>41000</v>
       </c>
       <c r="B341" t="n">
-        <v>0.425334722222222</v>
-      </c>
-      <c r="C341" t="n">
         <v>6.65622083333333</v>
       </c>
     </row>
@@ -4111,9 +3087,6 @@
         <v>41030</v>
       </c>
       <c r="B342" t="n">
-        <v>0.523353494623656</v>
-      </c>
-      <c r="C342" t="n">
         <v>7.40936021505376</v>
       </c>
     </row>
@@ -4122,9 +3095,6 @@
         <v>41061</v>
       </c>
       <c r="B343" t="n">
-        <v>0.513945833333333</v>
-      </c>
-      <c r="C343" t="n">
         <v>7.3209125</v>
       </c>
     </row>
@@ -4133,9 +3103,6 @@
         <v>41091</v>
       </c>
       <c r="B344" t="n">
-        <v>0.640719086021505</v>
-      </c>
-      <c r="C344" t="n">
         <v>8.31225403225806</v>
       </c>
     </row>
@@ -4144,9 +3111,6 @@
         <v>41122</v>
       </c>
       <c r="B345" t="n">
-        <v>0.721940860215054</v>
-      </c>
-      <c r="C345" t="n">
         <v>9.10403897849462</v>
       </c>
     </row>
@@ -4155,9 +3119,6 @@
         <v>41153</v>
       </c>
       <c r="B346" t="n">
-        <v>0.690847222222222</v>
-      </c>
-      <c r="C346" t="n">
         <v>8.89002916666667</v>
       </c>
     </row>
@@ -4166,9 +3127,6 @@
         <v>41183</v>
       </c>
       <c r="B347" t="n">
-        <v>0.695909825033647</v>
-      </c>
-      <c r="C347" t="n">
         <v>8.99663391655451</v>
       </c>
     </row>
@@ -4177,9 +3135,6 @@
         <v>41214</v>
       </c>
       <c r="B348" t="n">
-        <v>0.619170833333333</v>
-      </c>
-      <c r="C348" t="n">
         <v>8.24587083333333</v>
       </c>
     </row>
@@ -4188,9 +3143,6 @@
         <v>41244</v>
       </c>
       <c r="B349" t="n">
-        <v>0.604647849462366</v>
-      </c>
-      <c r="C349" t="n">
         <v>8.14929435483871</v>
       </c>
     </row>
@@ -4199,9 +3151,6 @@
         <v>41275</v>
       </c>
       <c r="B350" t="n">
-        <v>0.545638440860215</v>
-      </c>
-      <c r="C350" t="n">
         <v>7.65619489247312</v>
       </c>
     </row>
@@ -4210,9 +3159,6 @@
         <v>41306</v>
       </c>
       <c r="B351" t="n">
-        <v>0.57310119047619</v>
-      </c>
-      <c r="C351" t="n">
         <v>7.86833333333333</v>
       </c>
     </row>
@@ -4221,9 +3167,6 @@
         <v>41334</v>
       </c>
       <c r="B352" t="n">
-        <v>0.467495967741935</v>
-      </c>
-      <c r="C352" t="n">
         <v>7.02990053763441</v>
       </c>
     </row>
@@ -4232,9 +3175,6 @@
         <v>41365</v>
       </c>
       <c r="B353" t="n">
-        <v>0.348618055555556</v>
-      </c>
-      <c r="C353" t="n">
         <v>6.06884444444444</v>
       </c>
     </row>
@@ -4243,9 +3183,6 @@
         <v>41395</v>
       </c>
       <c r="B354" t="n">
-        <v>0.364569892473118</v>
-      </c>
-      <c r="C354" t="n">
         <v>6.18819086021505</v>
       </c>
     </row>
@@ -4254,9 +3191,6 @@
         <v>41426</v>
       </c>
       <c r="B355" t="n">
-        <v>0.431943055555556</v>
-      </c>
-      <c r="C355" t="n">
         <v>6.72647361111111</v>
       </c>
     </row>
@@ -4265,9 +3199,6 @@
         <v>41456</v>
       </c>
       <c r="B356" t="n">
-        <v>0.507795698924731</v>
-      </c>
-      <c r="C356" t="n">
         <v>7.29109408602151</v>
       </c>
     </row>
@@ -4276,9 +3207,6 @@
         <v>41487</v>
       </c>
       <c r="B357" t="n">
-        <v>0.651442204301075</v>
-      </c>
-      <c r="C357" t="n">
         <v>8.44252150537634</v>
       </c>
     </row>
@@ -4287,9 +3215,6 @@
         <v>41518</v>
       </c>
       <c r="B358" t="n">
-        <v>0.705684722222222</v>
-      </c>
-      <c r="C358" t="n">
         <v>9.03495138888889</v>
       </c>
     </row>
@@ -4298,9 +3223,6 @@
         <v>41548</v>
       </c>
       <c r="B359" t="n">
-        <v>0.68514535666218</v>
-      </c>
-      <c r="C359" t="n">
         <v>8.85462987886945</v>
       </c>
     </row>
@@ -4309,9 +3231,6 @@
         <v>41579</v>
       </c>
       <c r="B360" t="n">
-        <v>0.646497222222222</v>
-      </c>
-      <c r="C360" t="n">
         <v>8.417275</v>
       </c>
     </row>
@@ -4320,9 +3239,6 @@
         <v>41609</v>
       </c>
       <c r="B361" t="n">
-        <v>0.601719086021505</v>
-      </c>
-      <c r="C361" t="n">
         <v>8.04573655913978</v>
       </c>
     </row>
@@ -4331,9 +3247,6 @@
         <v>41640</v>
       </c>
       <c r="B362" t="n">
-        <v>0.577325268817204</v>
-      </c>
-      <c r="C362" t="n">
         <v>7.86499462365591</v>
       </c>
     </row>
@@ -4342,9 +3255,6 @@
         <v>41671</v>
       </c>
       <c r="B363" t="n">
-        <v>0.468949404761905</v>
-      </c>
-      <c r="C363" t="n">
         <v>7.00354910714286</v>
       </c>
     </row>
@@ -4353,9 +3263,6 @@
         <v>41699</v>
       </c>
       <c r="B364" t="n">
-        <v>0.39358064516129</v>
-      </c>
-      <c r="C364" t="n">
         <v>6.45073790322581</v>
       </c>
     </row>
@@ -4364,9 +3271,6 @@
         <v>41730</v>
       </c>
       <c r="B365" t="n">
-        <v>0.288931944444444</v>
-      </c>
-      <c r="C365" t="n">
         <v>5.67240416666667</v>
       </c>
     </row>
@@ -4375,9 +3279,6 @@
         <v>41760</v>
       </c>
       <c r="B366" t="n">
-        <v>0.306495967741935</v>
-      </c>
-      <c r="C366" t="n">
         <v>5.75036693548387</v>
       </c>
     </row>
@@ -4386,9 +3287,6 @@
         <v>41791</v>
       </c>
       <c r="B367" t="n">
-        <v>0.527297222222222</v>
-      </c>
-      <c r="C367" t="n">
         <v>7.42223611111111</v>
       </c>
     </row>
@@ -4397,9 +3295,6 @@
         <v>41821</v>
       </c>
       <c r="B368" t="n">
-        <v>0.601610215053763</v>
-      </c>
-      <c r="C368" t="n">
         <v>8.02069623655914</v>
       </c>
     </row>
@@ -4408,9 +3303,6 @@
         <v>41852</v>
       </c>
       <c r="B369" t="n">
-        <v>0.666791666666667</v>
-      </c>
-      <c r="C369" t="n">
         <v>8.57467204301075</v>
       </c>
     </row>
@@ -4419,9 +3311,6 @@
         <v>41883</v>
       </c>
       <c r="B370" t="n">
-        <v>0.6599875</v>
-      </c>
-      <c r="C370" t="n">
         <v>8.58812083333333</v>
       </c>
     </row>
@@ -4430,9 +3319,6 @@
         <v>41913</v>
       </c>
       <c r="B371" t="n">
-        <v>0.720585464333782</v>
-      </c>
-      <c r="C371" t="n">
         <v>9.18209690444145</v>
       </c>
     </row>
@@ -4441,9 +3327,6 @@
         <v>41944</v>
       </c>
       <c r="B372" t="n">
-        <v>0.623845833333333</v>
-      </c>
-      <c r="C372" t="n">
         <v>8.30375972222222</v>
       </c>
     </row>
@@ -4452,9 +3335,6 @@
         <v>41974</v>
       </c>
       <c r="B373" t="n">
-        <v>0.655994623655914</v>
-      </c>
-      <c r="C373" t="n">
         <v>8.49358198924731</v>
       </c>
     </row>
@@ -4463,9 +3343,6 @@
         <v>42005</v>
       </c>
       <c r="B374" t="n">
-        <v>0.596052419354839</v>
-      </c>
-      <c r="C374" t="n">
         <v>8.00607392473118</v>
       </c>
     </row>
@@ -4474,9 +3351,6 @@
         <v>42036</v>
       </c>
       <c r="B375" t="n">
-        <v>0.4815</v>
-      </c>
-      <c r="C375" t="n">
         <v>7.07069196428571</v>
       </c>
     </row>
@@ -4485,9 +3359,6 @@
         <v>42064</v>
       </c>
       <c r="B376" t="n">
-        <v>0.359129032258065</v>
-      </c>
-      <c r="C376" t="n">
         <v>6.14035215053763</v>
       </c>
     </row>
@@ -4496,9 +3367,6 @@
         <v>42095</v>
       </c>
       <c r="B377" t="n">
-        <v>0.348718055555556</v>
-      </c>
-      <c r="C377" t="n">
         <v>6.07014166666667</v>
       </c>
     </row>
@@ -4507,9 +3375,6 @@
         <v>42125</v>
       </c>
       <c r="B378" t="n">
-        <v>0.460975806451613</v>
-      </c>
-      <c r="C378" t="n">
         <v>6.95445967741936</v>
       </c>
     </row>
@@ -4518,9 +3383,6 @@
         <v>42156</v>
       </c>
       <c r="B379" t="n">
-        <v>0.508251388888889</v>
-      </c>
-      <c r="C379" t="n">
         <v>7.31051111111111</v>
       </c>
     </row>
@@ -4529,9 +3391,6 @@
         <v>42186</v>
       </c>
       <c r="B380" t="n">
-        <v>0.607096774193548</v>
-      </c>
-      <c r="C380" t="n">
         <v>8.12089516129032</v>
       </c>
     </row>
@@ -4540,9 +3399,6 @@
         <v>42217</v>
       </c>
       <c r="B381" t="n">
-        <v>0.679716397849462</v>
-      </c>
-      <c r="C381" t="n">
         <v>8.73075403225806</v>
       </c>
     </row>
@@ -4551,9 +3407,6 @@
         <v>42248</v>
       </c>
       <c r="B382" t="n">
-        <v>0.645583333333333</v>
-      </c>
-      <c r="C382" t="n">
         <v>8.47006388888889</v>
       </c>
     </row>
@@ -4562,9 +3415,6 @@
         <v>42278</v>
       </c>
       <c r="B383" t="n">
-        <v>0.680409152086137</v>
-      </c>
-      <c r="C383" t="n">
         <v>8.87520861372813</v>
       </c>
     </row>
@@ -4573,9 +3423,6 @@
         <v>42309</v>
       </c>
       <c r="B384" t="n">
-        <v>0.631076388888889</v>
-      </c>
-      <c r="C384" t="n">
         <v>8.35081805555556</v>
       </c>
     </row>
@@ -4584,9 +3431,6 @@
         <v>42339</v>
       </c>
       <c r="B385" t="n">
-        <v>0.609131720430108</v>
-      </c>
-      <c r="C385" t="n">
         <v>8.15546370967742</v>
       </c>
     </row>
@@ -4595,9 +3439,6 @@
         <v>42370</v>
       </c>
       <c r="B386" t="n">
-        <v>0.387243279569892</v>
-      </c>
-      <c r="C386" t="n">
         <v>6.41076612903226</v>
       </c>
     </row>
@@ -4606,9 +3447,6 @@
         <v>42401</v>
       </c>
       <c r="B387" t="n">
-        <v>0.425048850574713</v>
-      </c>
-      <c r="C387" t="n">
         <v>6.67477873563218</v>
       </c>
     </row>
@@ -4617,9 +3455,6 @@
         <v>42430</v>
       </c>
       <c r="B388" t="n">
-        <v>0.403731182795699</v>
-      </c>
-      <c r="C388" t="n">
         <v>6.5168185483871</v>
       </c>
     </row>
@@ -4628,9 +3463,6 @@
         <v>42461</v>
       </c>
       <c r="B389" t="n">
-        <v>0.480256944444444</v>
-      </c>
-      <c r="C389" t="n">
         <v>7.08847777777778</v>
       </c>
     </row>
@@ -4639,9 +3471,6 @@
         <v>42491</v>
       </c>
       <c r="B390" t="n">
-        <v>0.402372311827957</v>
-      </c>
-      <c r="C390" t="n">
         <v>6.50307258064516</v>
       </c>
     </row>
@@ -4650,9 +3479,6 @@
         <v>42522</v>
       </c>
       <c r="B391" t="n">
-        <v>0.511820833333333</v>
-      </c>
-      <c r="C391" t="n">
         <v>7.33847222222222</v>
       </c>
     </row>
@@ -4661,9 +3487,6 @@
         <v>42552</v>
       </c>
       <c r="B392" t="n">
-        <v>0.614084677419355</v>
-      </c>
-      <c r="C392" t="n">
         <v>8.17716532258065</v>
       </c>
     </row>
@@ -4672,9 +3495,6 @@
         <v>42583</v>
       </c>
       <c r="B393" t="n">
-        <v>0.605297043010753</v>
-      </c>
-      <c r="C393" t="n">
         <v>8.12407661290323</v>
       </c>
     </row>
@@ -4683,9 +3503,6 @@
         <v>42614</v>
       </c>
       <c r="B394" t="n">
-        <v>0.648720833333333</v>
-      </c>
-      <c r="C394" t="n">
         <v>8.53298888888889</v>
       </c>
     </row>
@@ -4694,9 +3511,6 @@
         <v>42644</v>
       </c>
       <c r="B395" t="n">
-        <v>0.718244952893674</v>
-      </c>
-      <c r="C395" t="n">
         <v>9.18246298788694</v>
       </c>
     </row>
@@ -4705,9 +3519,6 @@
         <v>42675</v>
       </c>
       <c r="B396" t="n">
-        <v>0.711865277777778</v>
-      </c>
-      <c r="C396" t="n">
         <v>9.09814027777778</v>
       </c>
     </row>
@@ -4716,9 +3527,6 @@
         <v>42705</v>
       </c>
       <c r="B397" t="n">
-        <v>0.629784946236559</v>
-      </c>
-      <c r="C397" t="n">
         <v>8.3048938172043</v>
       </c>
     </row>
@@ -4727,9 +3535,6 @@
         <v>42736</v>
       </c>
       <c r="B398" t="n">
-        <v>0.542290322580645</v>
-      </c>
-      <c r="C398" t="n">
         <v>7.56664650537634</v>
       </c>
     </row>
@@ -4738,9 +3543,6 @@
         <v>42767</v>
       </c>
       <c r="B399" t="n">
-        <v>0.45240625</v>
-      </c>
-      <c r="C399" t="n">
         <v>6.92108928571429</v>
       </c>
     </row>
@@ -4749,9 +3551,6 @@
         <v>42795</v>
       </c>
       <c r="B400" t="n">
-        <v>0.290547043010753</v>
-      </c>
-      <c r="C400" t="n">
         <v>5.65606586021505</v>
       </c>
     </row>
@@ -4760,9 +3559,6 @@
         <v>42826</v>
       </c>
       <c r="B401" t="n">
-        <v>0.342631944444444</v>
-      </c>
-      <c r="C401" t="n">
         <v>6.02930138888889</v>
       </c>
     </row>
@@ -4771,9 +3567,6 @@
         <v>42856</v>
       </c>
       <c r="B402" t="n">
-        <v>0.367388440860215</v>
-      </c>
-      <c r="C402" t="n">
         <v>6.20886290322581</v>
       </c>
     </row>
@@ -4782,9 +3575,6 @@
         <v>42887</v>
       </c>
       <c r="B403" t="n">
-        <v>0.540323611111111</v>
-      </c>
-      <c r="C403" t="n">
         <v>7.54589583333333</v>
       </c>
     </row>
@@ -4793,9 +3583,6 @@
         <v>42917</v>
       </c>
       <c r="B404" t="n">
-        <v>0.666688172043011</v>
-      </c>
-      <c r="C404" t="n">
         <v>8.6282997311828</v>
       </c>
     </row>
@@ -4804,9 +3591,6 @@
         <v>42948</v>
       </c>
       <c r="B405" t="n">
-        <v>0.618677419354839</v>
-      </c>
-      <c r="C405" t="n">
         <v>8.22268817204301</v>
       </c>
     </row>
@@ -4815,9 +3599,6 @@
         <v>42979</v>
       </c>
       <c r="B406" t="n">
-        <v>0.766704166666667</v>
-      </c>
-      <c r="C406" t="n">
         <v>9.63028333333333</v>
       </c>
     </row>
@@ -4826,9 +3607,6 @@
         <v>43009</v>
       </c>
       <c r="B407" t="n">
-        <v>0.730029609690444</v>
-      </c>
-      <c r="C407" t="n">
         <v>9.31753297442799</v>
       </c>
     </row>
@@ -4837,9 +3615,6 @@
         <v>43040</v>
       </c>
       <c r="B408" t="n">
-        <v>0.659502777777778</v>
-      </c>
-      <c r="C408" t="n">
         <v>8.61630833333333</v>
       </c>
     </row>
@@ -4848,9 +3623,6 @@
         <v>43070</v>
       </c>
       <c r="B409" t="n">
-        <v>0.631909946236559</v>
-      </c>
-      <c r="C409" t="n">
         <v>8.26272043010753</v>
       </c>
     </row>
@@ -4859,9 +3631,6 @@
         <v>43101</v>
       </c>
       <c r="B410" t="n">
-        <v>0.517021505376344</v>
-      </c>
-      <c r="C410" t="n">
         <v>7.41355376344086</v>
       </c>
     </row>
@@ -4870,9 +3639,6 @@
         <v>43132</v>
       </c>
       <c r="B411" t="n">
-        <v>0.351488095238095</v>
-      </c>
-      <c r="C411" t="n">
         <v>6.03053422619048</v>
       </c>
     </row>
@@ -4881,9 +3647,6 @@
         <v>43160</v>
       </c>
       <c r="B412" t="n">
-        <v>0.350220430107527</v>
-      </c>
-      <c r="C412" t="n">
         <v>6.04907392473118</v>
       </c>
     </row>
@@ -4892,9 +3655,6 @@
         <v>43191</v>
       </c>
       <c r="B413" t="n">
-        <v>0.298120833333333</v>
-      </c>
-      <c r="C413" t="n">
         <v>5.60403888888889</v>
       </c>
     </row>
@@ -4903,9 +3663,6 @@
         <v>43221</v>
       </c>
       <c r="B414" t="n">
-        <v>0.381581989247312</v>
-      </c>
-      <c r="C414" t="n">
         <v>6.33354032258065</v>
       </c>
     </row>
@@ -4914,9 +3671,6 @@
         <v>43252</v>
       </c>
       <c r="B415" t="n">
-        <v>0.548194444444444</v>
-      </c>
-      <c r="C415" t="n">
         <v>7.57977916666667</v>
       </c>
     </row>
@@ -4925,9 +3679,6 @@
         <v>43282</v>
       </c>
       <c r="B416" t="n">
-        <v>0.564280913978495</v>
-      </c>
-      <c r="C416" t="n">
         <v>7.70575806451613</v>
       </c>
     </row>
@@ -4936,9 +3687,6 @@
         <v>43313</v>
       </c>
       <c r="B417" t="n">
-        <v>0.60004435483871</v>
-      </c>
-      <c r="C417" t="n">
         <v>8.04276478494624</v>
       </c>
     </row>
@@ -4947,9 +3695,6 @@
         <v>43344</v>
       </c>
       <c r="B418" t="n">
-        <v>0.693301388888889</v>
-      </c>
-      <c r="C418" t="n">
         <v>8.91461944444444</v>
       </c>
     </row>
@@ -4958,9 +3703,6 @@
         <v>43374</v>
       </c>
       <c r="B419" t="n">
-        <v>0.637547043010753</v>
-      </c>
-      <c r="C419" t="n">
         <v>8.48869489247312</v>
       </c>
     </row>
@@ -4969,9 +3711,6 @@
         <v>43405</v>
       </c>
       <c r="B420" t="n">
-        <v>0.711087621696801</v>
-      </c>
-      <c r="C420" t="n">
         <v>9.04012656467316</v>
       </c>
     </row>
@@ -4980,9 +3719,6 @@
         <v>43435</v>
       </c>
       <c r="B421" t="n">
-        <v>0.521456989247312</v>
-      </c>
-      <c r="C421" t="n">
         <v>7.41711827956989</v>
       </c>
     </row>
@@ -4991,9 +3727,6 @@
         <v>43466</v>
       </c>
       <c r="B422" t="n">
-        <v>0.430251344086022</v>
-      </c>
-      <c r="C422" t="n">
         <v>6.70752016129032</v>
       </c>
     </row>
@@ -5002,9 +3735,6 @@
         <v>43497</v>
       </c>
       <c r="B423" t="n">
-        <v>0.3126875</v>
-      </c>
-      <c r="C423" t="n">
         <v>5.7666369047619</v>
       </c>
     </row>
@@ -5013,9 +3743,6 @@
         <v>43525</v>
       </c>
       <c r="B424" t="n">
-        <v>0.263340053763441</v>
-      </c>
-      <c r="C424" t="n">
         <v>5.38700940860215</v>
       </c>
     </row>
@@ -5024,9 +3751,6 @@
         <v>43556</v>
       </c>
       <c r="B425" t="n">
-        <v>0.274276388888889</v>
-      </c>
-      <c r="C425" t="n">
         <v>5.48471111111111</v>
       </c>
     </row>
@@ -5035,9 +3759,6 @@
         <v>43586</v>
       </c>
       <c r="B426" t="n">
-        <v>0.409572580645161</v>
-      </c>
-      <c r="C426" t="n">
         <v>6.53885215053763</v>
       </c>
     </row>
@@ -5046,9 +3767,6 @@
         <v>43617</v>
       </c>
       <c r="B427" t="n">
-        <v>0.518627777777778</v>
-      </c>
-      <c r="C427" t="n">
         <v>7.38718472222222</v>
       </c>
     </row>
@@ -5057,9 +3775,6 @@
         <v>43647</v>
       </c>
       <c r="B428" t="n">
-        <v>0.556904569892473</v>
-      </c>
-      <c r="C428" t="n">
         <v>7.66298655913979</v>
       </c>
     </row>
@@ -5068,9 +3783,6 @@
         <v>43678</v>
       </c>
       <c r="B429" t="n">
-        <v>0.671708333333333</v>
-      </c>
-      <c r="C429" t="n">
         <v>8.68789650537634</v>
       </c>
     </row>
@@ -5079,9 +3791,6 @@
         <v>43709</v>
       </c>
       <c r="B430" t="n">
-        <v>0.659502777777778</v>
-      </c>
-      <c r="C430" t="n">
         <v>8.64098611111111</v>
       </c>
     </row>
@@ -5090,9 +3799,6 @@
         <v>43739</v>
       </c>
       <c r="B431" t="n">
-        <v>0.65166935483871</v>
-      </c>
-      <c r="C431" t="n">
         <v>8.65729166666667</v>
       </c>
     </row>
@@ -5101,9 +3807,6 @@
         <v>43770</v>
       </c>
       <c r="B432" t="n">
-        <v>0.623279166666667</v>
-      </c>
-      <c r="C432" t="n">
         <v>8.32084583333333</v>
       </c>
     </row>
@@ -5112,9 +3815,6 @@
         <v>43800</v>
       </c>
       <c r="B433" t="n">
-        <v>0.584112903225806</v>
-      </c>
-      <c r="C433" t="n">
         <v>8.01311693548387</v>
       </c>
     </row>
@@ -5123,9 +3823,6 @@
         <v>43831</v>
       </c>
       <c r="B434" t="n">
-        <v>0.40114247311828</v>
-      </c>
-      <c r="C434" t="n">
         <v>6.48355376344086</v>
       </c>
     </row>
@@ -5134,9 +3831,6 @@
         <v>43862</v>
       </c>
       <c r="B435" t="n">
-        <v>0.315989942528736</v>
-      </c>
-      <c r="C435" t="n">
         <v>5.80689224137931</v>
       </c>
     </row>
@@ -5145,9 +3839,6 @@
         <v>43891</v>
       </c>
       <c r="B436" t="n">
-        <v>0.210209677419355</v>
-      </c>
-      <c r="C436" t="n">
         <v>4.86359139784946</v>
       </c>
     </row>
@@ -5156,9 +3847,6 @@
         <v>43922</v>
       </c>
       <c r="B437" t="n">
-        <v>0.261219444444444</v>
-      </c>
-      <c r="C437" t="n">
         <v>5.42717083333333</v>
       </c>
     </row>
@@ -5167,9 +3855,6 @@
         <v>43952</v>
       </c>
       <c r="B438" t="n">
-        <v>0.34965188172043</v>
-      </c>
-      <c r="C438" t="n">
         <v>6.10531451612903</v>
       </c>
     </row>
@@ -5178,9 +3863,6 @@
         <v>43983</v>
       </c>
       <c r="B439" t="n">
-        <v>0.478773611111111</v>
-      </c>
-      <c r="C439" t="n">
         <v>7.09603472222222</v>
       </c>
     </row>
@@ -5189,9 +3871,6 @@
         <v>44013</v>
       </c>
       <c r="B440" t="n">
-        <v>0.523813172043011</v>
-      </c>
-      <c r="C440" t="n">
         <v>7.40172043010753</v>
       </c>
     </row>
@@ -5200,9 +3879,6 @@
         <v>44044</v>
       </c>
       <c r="B441" t="n">
-        <v>0.615188172043011</v>
-      </c>
-      <c r="C441" t="n">
         <v>8.18094220430108</v>
       </c>
     </row>
@@ -5211,9 +3887,6 @@
         <v>44075</v>
       </c>
       <c r="B442" t="n">
-        <v>0.615413888888889</v>
-      </c>
-      <c r="C442" t="n">
         <v>8.24843472222222</v>
       </c>
     </row>
@@ -5222,9 +3895,6 @@
         <v>44105</v>
       </c>
       <c r="B443" t="n">
-        <v>0.618466397849462</v>
-      </c>
-      <c r="C443" t="n">
         <v>8.25507930107527</v>
       </c>
     </row>
@@ -5233,9 +3903,6 @@
         <v>44136</v>
       </c>
       <c r="B444" t="n">
-        <v>0.590044444444444</v>
-      </c>
-      <c r="C444" t="n">
         <v>7.99225416666667</v>
       </c>
     </row>
@@ -5244,9 +3911,6 @@
         <v>44166</v>
       </c>
       <c r="B445" t="n">
-        <v>0.591623149394347</v>
-      </c>
-      <c r="C445" t="n">
         <v>8.00940242261104</v>
       </c>
     </row>
@@ -5255,9 +3919,6 @@
         <v>44197</v>
       </c>
       <c r="B446" t="n">
-        <v>0.483833333333333</v>
-      </c>
-      <c r="C446" t="n">
         <v>7.1717123655914</v>
       </c>
     </row>
@@ -5266,9 +3927,6 @@
         <v>44228</v>
       </c>
       <c r="B447" t="n">
-        <v>0.404272321428571</v>
-      </c>
-      <c r="C447" t="n">
         <v>6.49723363095238</v>
       </c>
     </row>
@@ -5277,9 +3935,6 @@
         <v>44256</v>
       </c>
       <c r="B448" t="n">
-        <v>0.333618279569892</v>
-      </c>
-      <c r="C448" t="n">
         <v>5.92032661290323</v>
       </c>
     </row>
@@ -5288,9 +3943,6 @@
         <v>44287</v>
       </c>
       <c r="B449" t="n">
-        <v>0.330834722222222</v>
-      </c>
-      <c r="C449" t="n">
         <v>5.96486666666667</v>
       </c>
     </row>
@@ -5299,9 +3951,6 @@
         <v>44317</v>
       </c>
       <c r="B450" t="n">
-        <v>0.334666666666667</v>
-      </c>
-      <c r="C450" t="n">
         <v>5.92118682795699</v>
       </c>
     </row>
@@ -5310,9 +3959,6 @@
         <v>44348</v>
       </c>
       <c r="B451" t="n">
-        <v>0.3214</v>
-      </c>
-      <c r="C451" t="n">
         <v>5.81406388888889</v>
       </c>
     </row>
@@ -5321,9 +3967,6 @@
         <v>44378</v>
       </c>
       <c r="B452" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="C452" t="n">
         <v>7.02259811827957</v>
       </c>
     </row>
@@ -5332,9 +3975,6 @@
         <v>44409</v>
       </c>
       <c r="B453" t="n">
-        <v>0.622978494623656</v>
-      </c>
-      <c r="C453" t="n">
         <v>8.22106720430108</v>
       </c>
     </row>
@@ -5343,9 +3983,6 @@
         <v>44440</v>
       </c>
       <c r="B454" t="n">
-        <v>0.593363888888889</v>
-      </c>
-      <c r="C454" t="n">
         <v>8.04637361111111</v>
       </c>
     </row>
@@ -5354,9 +3991,6 @@
         <v>44470</v>
       </c>
       <c r="B455" t="n">
-        <v>0.599556451612903</v>
-      </c>
-      <c r="C455" t="n">
         <v>8.12182795698925</v>
       </c>
     </row>
@@ -5365,9 +3999,6 @@
         <v>44501</v>
       </c>
       <c r="B456" t="n">
-        <v>0.581065277777778</v>
-      </c>
-      <c r="C456" t="n">
         <v>7.9751375</v>
       </c>
     </row>
@@ -5376,9 +4007,6 @@
         <v>44531</v>
       </c>
       <c r="B457" t="n">
-        <v>0.565873655913979</v>
-      </c>
-      <c r="C457" t="n">
         <v>7.81816666666667</v>
       </c>
     </row>
@@ -5387,9 +4015,6 @@
         <v>44562</v>
       </c>
       <c r="B458" t="n">
-        <v>0.353741935483871</v>
-      </c>
-      <c r="C458" t="n">
         <v>6.13458333333333</v>
       </c>
     </row>
@@ -5398,9 +4023,6 @@
         <v>44593</v>
       </c>
       <c r="B459" t="n">
-        <v>0.369354166666667</v>
-      </c>
-      <c r="C459" t="n">
         <v>6.26226041666667</v>
       </c>
     </row>
@@ -5409,9 +4031,6 @@
         <v>44621</v>
       </c>
       <c r="B460" t="n">
-        <v>0.270885752688172</v>
-      </c>
-      <c r="C460" t="n">
         <v>5.48906989247312</v>
       </c>
     </row>
@@ -5420,9 +4039,6 @@
         <v>44652</v>
       </c>
       <c r="B461" t="n">
-        <v>0.2620375</v>
-      </c>
-      <c r="C461" t="n">
         <v>5.39392638888889</v>
       </c>
     </row>
@@ -5431,9 +4047,6 @@
         <v>44682</v>
       </c>
       <c r="B462" t="n">
-        <v>0.310274193548387</v>
-      </c>
-      <c r="C462" t="n">
         <v>5.73096908602151</v>
       </c>
     </row>
@@ -5442,9 +4055,6 @@
         <v>44713</v>
       </c>
       <c r="B463" t="n">
-        <v>0.374038888888889</v>
-      </c>
-      <c r="C463" t="n">
         <v>6.2402</v>
       </c>
     </row>
@@ -5453,9 +4063,6 @@
         <v>44743</v>
       </c>
       <c r="B464" t="n">
-        <v>0.563478494623656</v>
-      </c>
-      <c r="C464" t="n">
         <v>7.71624193548387</v>
       </c>
     </row>
@@ -5464,9 +4071,6 @@
         <v>44774</v>
       </c>
       <c r="B465" t="n">
-        <v>0.587766129032258</v>
-      </c>
-      <c r="C465" t="n">
         <v>7.91600134408602</v>
       </c>
     </row>
@@ -5475,9 +4079,6 @@
         <v>44805</v>
       </c>
       <c r="B466" t="n">
-        <v>0.580640277777778</v>
-      </c>
-      <c r="C466" t="n">
         <v>7.94815277777778</v>
       </c>
     </row>
@@ -5486,9 +4087,6 @@
         <v>44835</v>
       </c>
       <c r="B467" t="n">
-        <v>0.632998655913979</v>
-      </c>
-      <c r="C467" t="n">
         <v>8.43850268817204</v>
       </c>
     </row>
@@ -5497,9 +4095,6 @@
         <v>44866</v>
       </c>
       <c r="B468" t="n">
-        <v>0.463176388888889</v>
-      </c>
-      <c r="C468" t="n">
         <v>6.97203472222222</v>
       </c>
     </row>
@@ -5508,9 +4103,6 @@
         <v>44896</v>
       </c>
       <c r="B469" t="n">
-        <v>0.508189516129032</v>
-      </c>
-      <c r="C469" t="n">
         <v>7.33165725806452</v>
       </c>
     </row>
@@ -5519,9 +4111,6 @@
         <v>44927</v>
       </c>
       <c r="B470" t="n">
-        <v>0.425591397849462</v>
-      </c>
-      <c r="C470" t="n">
         <v>6.68067876344086</v>
       </c>
     </row>
@@ -5530,9 +4119,6 @@
         <v>44958</v>
       </c>
       <c r="B471" t="n">
-        <v>0.400745535714286</v>
-      </c>
-      <c r="C471" t="n">
         <v>6.461</v>
       </c>
     </row>
@@ -5541,9 +4127,6 @@
         <v>44986</v>
       </c>
       <c r="B472" t="n">
-        <v>0.289875</v>
-      </c>
-      <c r="C472" t="n">
         <v>5.49804166666667</v>
       </c>
     </row>
@@ -5552,9 +4135,6 @@
         <v>45017</v>
       </c>
       <c r="B473" t="n">
-        <v>0.2145</v>
-      </c>
-      <c r="C473" t="n">
         <v>4.83299166666667</v>
       </c>
     </row>
@@ -5563,9 +4143,6 @@
         <v>45047</v>
       </c>
       <c r="B474" t="n">
-        <v>0.320994623655914</v>
-      </c>
-      <c r="C474" t="n">
         <v>5.85291129032258</v>
       </c>
     </row>
@@ -5574,9 +4151,6 @@
         <v>45078</v>
       </c>
       <c r="B475" t="n">
-        <v>0.461388888888889</v>
-      </c>
-      <c r="C475" t="n">
         <v>6.95813333333333</v>
       </c>
     </row>
@@ -5585,9 +4159,6 @@
         <v>45108</v>
       </c>
       <c r="B476" t="n">
-        <v>0.532120967741936</v>
-      </c>
-      <c r="C476" t="n">
         <v>7.46910483870968</v>
       </c>
     </row>
@@ -5596,9 +4167,6 @@
         <v>45139</v>
       </c>
       <c r="B477" t="n">
-        <v>0.531837365591398</v>
-      </c>
-      <c r="C477" t="n">
         <v>7.51409005376344</v>
       </c>
     </row>
@@ -5607,9 +4175,6 @@
         <v>45170</v>
       </c>
       <c r="B478" t="n">
-        <v>0.660276388888889</v>
-      </c>
-      <c r="C478" t="n">
         <v>8.56523055555556</v>
       </c>
     </row>
@@ -5618,9 +4183,6 @@
         <v>45200</v>
       </c>
       <c r="B479" t="n">
-        <v>0.591122311827957</v>
-      </c>
-      <c r="C479" t="n">
         <v>8.01814784946237</v>
       </c>
     </row>
@@ -5629,9 +4191,6 @@
         <v>45231</v>
       </c>
       <c r="B480" t="n">
-        <v>0.576755555555556</v>
-      </c>
-      <c r="C480" t="n">
         <v>7.93992777777778</v>
       </c>
     </row>
@@ -5640,9 +4199,6 @@
         <v>45261</v>
       </c>
       <c r="B481" t="n">
-        <v>0.505846774193548</v>
-      </c>
-      <c r="C481" t="n">
         <v>7.31477822580645</v>
       </c>
     </row>
